--- a/src/attributions/attributions_saliency_traj_455.xlsx
+++ b/src/attributions/attributions_saliency_traj_455.xlsx
@@ -2137,2278 +2137,2278 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0003934449923690408</v>
+        <v>0.007730714045464993</v>
       </c>
       <c r="B4" t="n">
-        <v>0.002071491675451398</v>
+        <v>0.003988121636211872</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0003376416862010956</v>
+        <v>5.603337194770575e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003449016949161887</v>
+        <v>0.001391919795423746</v>
       </c>
       <c r="E4" t="n">
-        <v>5.013062764192e-05</v>
+        <v>0.001308866078034043</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00226961774751544</v>
+        <v>0.0130060501396656</v>
       </c>
       <c r="G4" t="n">
-        <v>4.655387601815164e-05</v>
+        <v>0.001426584785804152</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0001694894599495456</v>
+        <v>0.004421467427164316</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002495301887392998</v>
+        <v>0.002689087763428688</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0009589236578904092</v>
+        <v>0.005913021042943001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001148900832049549</v>
+        <v>0.008680736646056175</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003891598316840827</v>
+        <v>0.0002253084676340222</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0004138941003475338</v>
+        <v>0.000408249266911298</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001301066513406113</v>
+        <v>0.001801035832613707</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00142328254878521</v>
+        <v>0.01063493452966213</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0004524223040789366</v>
+        <v>0.006257158238440752</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0002370750298723578</v>
+        <v>0.003419957822188735</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0002001995890168473</v>
+        <v>4.559417720884085e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>2.41536272369558e-05</v>
+        <v>0.001318207010626793</v>
       </c>
       <c r="T4" t="n">
-        <v>0.000373601564206183</v>
+        <v>0.00540572963654995</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0002652652910910547</v>
+        <v>0.004346904344856739</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0002676219737622887</v>
+        <v>0.001511772046796978</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0006341937114484608</v>
+        <v>0.004697827156633139</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0001162587432190776</v>
+        <v>0.005004098173230886</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002938225516118109</v>
+        <v>0.004706967622041702</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0002584964095149189</v>
+        <v>0.002033833414316177</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.768681436777115e-05</v>
+        <v>0.001765630673617125</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0003641365619841963</v>
+        <v>0.001502848463132977</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0001267552142962813</v>
+        <v>0.0008675095741637051</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0005074295331723988</v>
+        <v>0.003360158065333962</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0001995035854633898</v>
+        <v>0.0001425885129719973</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0004125573323108256</v>
+        <v>0.0002380285295657814</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0001565470884088427</v>
+        <v>0.0006644882378168404</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0003547280211932957</v>
+        <v>0.0004605754220392555</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.759337363997474e-05</v>
+        <v>0.005199290346354246</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.0002431983157293871</v>
+        <v>0.00247159437276423</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.599969229777344e-05</v>
+        <v>7.116049528121948e-05</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.704089951701462e-05</v>
+        <v>0.000301324762403965</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0003151000419165939</v>
+        <v>0.000665664323605597</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.000346048705978319</v>
+        <v>0.002448322018608451</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.000189982180017978</v>
+        <v>0.00417700968682766</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0003942459297832102</v>
+        <v>0.003031087573617697</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.0002905030269175768</v>
+        <v>0.002307606162503362</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.500360465608537e-05</v>
+        <v>0.002721005352213979</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0003343503922224045</v>
+        <v>0.001785733853466809</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.0001149508680100553</v>
+        <v>0.0007607146399095654</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.0007912238361313939</v>
+        <v>0.01250842772424221</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.000650580448564142</v>
+        <v>0.001295529305934906</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.0003802652645390481</v>
+        <v>0.0001029116247082129</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0004233840445522219</v>
+        <v>0.0001837390009313822</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.0007823717314749956</v>
+        <v>0.00808296725153923</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.00052725023124367</v>
+        <v>0.000724520708899945</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.0002448020677547902</v>
+        <v>0.002982174511998892</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.000838149746414274</v>
+        <v>0.0008551071514375508</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0006484334589913487</v>
+        <v>0.006647640839219093</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0004306035698391497</v>
+        <v>7.031729910522699e-05</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.000398257514461875</v>
+        <v>0.002000500448048115</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.0001911623548949137</v>
+        <v>0.001978847663849592</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.0001402994676027447</v>
+        <v>0.001278367592021823</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0009994584834203124</v>
+        <v>0.001599877141416073</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0005918316310271621</v>
+        <v>0.0003459709696471691</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.0002212893741670996</v>
+        <v>0.006127605680376291</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.00038866326212883</v>
+        <v>0.001054827705956995</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0001251539069926366</v>
+        <v>0.002584486268460751</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.0002530459896661341</v>
+        <v>0.003845163155347109</v>
       </c>
       <c r="BN4" t="n">
-        <v>8.515642548445612e-06</v>
+        <v>0.00105346692726016</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.0001140229724114761</v>
+        <v>9.122519986703992e-05</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0004110350855626166</v>
+        <v>0.002349243266507983</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0001695224636932835</v>
+        <v>0.003299365751445293</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.0002183815668104216</v>
+        <v>0.001578207476995885</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.0002212248073192313</v>
+        <v>0.002578631741926074</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.0003482747415546328</v>
+        <v>0.0005526902968995273</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.405913543654606e-05</v>
+        <v>0.001175935380160809</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.0004820508765988052</v>
+        <v>0.001080851652659476</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0004420895129442215</v>
+        <v>0.003011773340404034</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0001965199480764568</v>
+        <v>0.005863672588020563</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0005842284299433231</v>
+        <v>0.002982171718031168</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.047396214446053e-05</v>
+        <v>0.007195969577878714</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.85943232383579e-05</v>
+        <v>0.00211434718221426</v>
       </c>
       <c r="CB4" t="n">
-        <v>8.161542791640386e-05</v>
+        <v>0.0009139560861513019</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.0001892690343083814</v>
+        <v>0.00077532057184726</v>
       </c>
       <c r="CD4" t="n">
-        <v>8.551357313990593e-05</v>
+        <v>9.487514034844935e-05</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0001987163559533656</v>
+        <v>0.001551589230075479</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.000242550071561709</v>
+        <v>0.001197710866108537</v>
       </c>
       <c r="CG4" t="n">
-        <v>1.300505755352788e-05</v>
+        <v>0.001092703780159354</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.000200736103579402</v>
+        <v>0.000417071976698935</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.0003792134812101722</v>
+        <v>0.003002328798174858</v>
       </c>
       <c r="CJ4" t="n">
-        <v>3.349470352986827e-05</v>
+        <v>0.0006366332527250051</v>
       </c>
       <c r="CK4" t="n">
-        <v>8.108003385132179e-06</v>
+        <v>0.001333500957116485</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.0002536717220209539</v>
+        <v>0.001349225640296936</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.000253476551733911</v>
+        <v>0.0009784119902178645</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0005776843172498047</v>
+        <v>0.006573667749762535</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.0003988899989053607</v>
+        <v>0.0001841719495132565</v>
       </c>
       <c r="CP4" t="n">
-        <v>8.939503459259868e-05</v>
+        <v>0.0003943925548810512</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.0001256355026271194</v>
+        <v>0.002281397115439177</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.790506757970434e-06</v>
+        <v>0.002654635347425938</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.242610207758844e-05</v>
+        <v>0.003835339797660708</v>
       </c>
       <c r="CT4" t="n">
-        <v>7.328154606511816e-05</v>
+        <v>0.00268214475363493</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0005581217701546848</v>
+        <v>0.0001182634732685983</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.061155126080848e-05</v>
+        <v>0.0003194289747625589</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.000243897462496534</v>
+        <v>0.001157495426014066</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.000206084267119877</v>
+        <v>0.0004483681987039745</v>
       </c>
       <c r="CY4" t="n">
-        <v>8.095448720268905e-05</v>
+        <v>0.001214697258546948</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0002328511909581721</v>
+        <v>0.0009809398325160146</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0002955412783194333</v>
+        <v>0.00261925021186471</v>
       </c>
       <c r="DB4" t="n">
-        <v>9.145709191216156e-05</v>
+        <v>0.0003545516519807279</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.08799792744685e-05</v>
+        <v>0.0003441995359025896</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0002497965178918093</v>
+        <v>0.0006377497338689864</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.0002928765898104757</v>
+        <v>0.002983439713716507</v>
       </c>
       <c r="DF4" t="n">
-        <v>7.136109343264252e-05</v>
+        <v>0.00119450269266963</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.0001817728480091318</v>
+        <v>0.00117675110232085</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.0005777712212875485</v>
+        <v>0.0001546390412840992</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0001254158123629168</v>
+        <v>0.002165164332836866</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.001133530866354704</v>
+        <v>0.006257781758904457</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0003605475649237633</v>
+        <v>0.001708031282760203</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0002646850189194083</v>
+        <v>0.002395080868154764</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0009376072557643056</v>
+        <v>0.002412267494946718</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.000297470367513597</v>
+        <v>0.001169550465419888</v>
       </c>
       <c r="DO4" t="n">
-        <v>5.121003778185695e-05</v>
+        <v>0.0008120262646116316</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.0001641056296648458</v>
+        <v>0.002502960851415992</v>
       </c>
       <c r="DQ4" t="n">
-        <v>2.096158459607977e-05</v>
+        <v>0.004360704217106104</v>
       </c>
       <c r="DR4" t="n">
-        <v>4.494551103562117e-05</v>
+        <v>0.001479541417211294</v>
       </c>
       <c r="DS4" t="n">
-        <v>8.11084610177204e-05</v>
+        <v>0.003391939681023359</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.0002612329553812742</v>
+        <v>0.001534533803351223</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.0001049498459906317</v>
+        <v>8.578025153838098e-05</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.0003538626478984952</v>
+        <v>0.0004130414454266429</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0001963581598829478</v>
+        <v>0.001377275446429849</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.0002325182140339166</v>
+        <v>0.002154579851776361</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.057735299691558e-05</v>
+        <v>0.00118519552052021</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0002955662785097957</v>
+        <v>0.0009020980214700103</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.0002482035779394209</v>
+        <v>0.003616320434957743</v>
       </c>
       <c r="EB4" t="n">
-        <v>2.006746581173502e-05</v>
+        <v>0.000142645847517997</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.734425652306527e-05</v>
+        <v>0.0009068888030014932</v>
       </c>
       <c r="ED4" t="n">
-        <v>3.552626367309131e-05</v>
+        <v>0.00463140569627285</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0003275510389357805</v>
+        <v>0.003838346805423498</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0001295960391871631</v>
+        <v>0.001604392658919096</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.0002509226324036717</v>
+        <v>0.001778685487806797</v>
       </c>
       <c r="EH4" t="n">
-        <v>9.666533878771588e-05</v>
+        <v>0.00196762615814805</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.0003817084361799061</v>
+        <v>0.0009479231666773558</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0002594073012005538</v>
+        <v>0.002747891005128622</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.000152018474182114</v>
+        <v>0.002679816912859678</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0002180176961701363</v>
+        <v>0.0004013300931546837</v>
       </c>
       <c r="EM4" t="n">
-        <v>7.147734140744433e-05</v>
+        <v>0.0001981751265702769</v>
       </c>
       <c r="EN4" t="n">
-        <v>4.774260014528409e-05</v>
+        <v>0.001252556452527642</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.0002186656929552555</v>
+        <v>0.0005421272944658995</v>
       </c>
       <c r="EP4" t="n">
-        <v>7.640934200026095e-06</v>
+        <v>0.0005756424507126212</v>
       </c>
       <c r="EQ4" t="n">
-        <v>4.232909850543365e-05</v>
+        <v>0.003092319238930941</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.000216581072891131</v>
+        <v>0.001407351344823837</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0004886866663582623</v>
+        <v>0.001983274472877383</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0006796382949687541</v>
+        <v>0.004739060997962952</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.0002194731205236167</v>
+        <v>0.0002240162575617433</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0003349332837387919</v>
+        <v>0.0008599462453275919</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.0005500525003299117</v>
+        <v>9.82912170002237e-05</v>
       </c>
       <c r="EX4" t="n">
-        <v>2.063685315079056e-05</v>
+        <v>0.0006718907970935106</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0002530852216295898</v>
+        <v>0.001470419811084867</v>
       </c>
       <c r="EZ4" t="n">
-        <v>9.656502516008914e-05</v>
+        <v>0.0001639834081288427</v>
       </c>
       <c r="FA4" t="n">
-        <v>2.751888678176329e-05</v>
+        <v>0.001679594977758825</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.0002595644618850201</v>
+        <v>0.001710881246253848</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.0002025167195824906</v>
+        <v>0.002837661188095808</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.0001238853292306885</v>
+        <v>0.0005734922597184777</v>
       </c>
       <c r="FE4" t="n">
-        <v>8.134840754792094e-05</v>
+        <v>0.0008426897111348808</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.000370009511243552</v>
+        <v>0.000763924210332334</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.0003295838250778615</v>
+        <v>0.002441615099087358</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.0001076323096640408</v>
+        <v>0.0008107683388516307</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.0001771217066561803</v>
+        <v>0.0003224237007088959</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.0004149602318648249</v>
+        <v>4.597051884047687e-05</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.0002051220944849774</v>
+        <v>0.003624287201091647</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.0004186482692603022</v>
+        <v>0.0001004695659503341</v>
       </c>
       <c r="FM4" t="n">
-        <v>6.891589146107435e-05</v>
+        <v>0.0009637346956878901</v>
       </c>
       <c r="FN4" t="n">
-        <v>2.610620867926627e-06</v>
+        <v>0.001719306921586394</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.0002482180716469884</v>
+        <v>0.002209623577073216</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.0002061606937786564</v>
+        <v>0.004935628734529018</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.0003733740013558418</v>
+        <v>0.001329999417066574</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.0002710531989578158</v>
+        <v>0.002718646079301834</v>
       </c>
       <c r="FS4" t="n">
-        <v>8.529034676030278e-05</v>
+        <v>0.0005589162465184927</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0003752139455173165</v>
+        <v>0.006566047668457031</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.0008855243213474751</v>
+        <v>0.001254638773389161</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.0001264480961253867</v>
+        <v>0.006384887732565403</v>
       </c>
       <c r="FW4" t="n">
-        <v>7.566290150862187e-05</v>
+        <v>0.00375563045963645</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.0003541896585375071</v>
+        <v>0.0003938662121072412</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.0004519106587395072</v>
+        <v>0.002607123460620642</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.0001679006236372516</v>
+        <v>0.002222498413175344</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.0001747161441016942</v>
+        <v>0.0009863789891824126</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.0003674781764857471</v>
+        <v>0.001029703766107559</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.0005305140512064099</v>
+        <v>0.003897334448993206</v>
       </c>
       <c r="GD4" t="n">
-        <v>7.510873547289521e-05</v>
+        <v>0.003290862310677767</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.0001061673174262978</v>
+        <v>0.001972923055291176</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.0003151371201965958</v>
+        <v>7.262523286044598e-05</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.0004010459815617651</v>
+        <v>0.001348491990938783</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.001489549060352147</v>
+        <v>0.0004697804688476026</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02166050113737583</v>
+        <v>0.004579579457640648</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0005870512104593217</v>
+        <v>0.0009544693748466671</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01689957641065121</v>
+        <v>0.002877396764233708</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009286306798458099</v>
+        <v>0.0001783109619282186</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004130248911678791</v>
+        <v>0.001882501761429012</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003695361549034715</v>
+        <v>0.001568872714415193</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003885621204972267</v>
+        <v>0.00157775531988591</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004390710033476353</v>
+        <v>0.0002249458048027009</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003150663804262877</v>
+        <v>0.0008526822784915566</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01579966954886913</v>
+        <v>0.004480190575122833</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001684540417045355</v>
+        <v>0.001789917703717947</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01581253297626972</v>
+        <v>0.003868531435728073</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01511648297309875</v>
+        <v>0.0008171715307980776</v>
       </c>
       <c r="O5" t="n">
-        <v>0.007707635872066021</v>
+        <v>0.001861945493146777</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001416590646840632</v>
+        <v>0.001752752927131951</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001677513471804559</v>
+        <v>0.0008521467680111527</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004706772044301033</v>
+        <v>0.0005115349777042866</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0009903471218422055</v>
+        <v>2.600033622002229e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002368583576753736</v>
+        <v>0.0003786271845456213</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0005962182767689228</v>
+        <v>0.0001443507353542373</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003483375301584601</v>
+        <v>0.0002347644331166521</v>
       </c>
       <c r="W5" t="n">
-        <v>0.00726094376295805</v>
+        <v>6.295435014180839e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>9.494955884292722e-05</v>
+        <v>0.0007004488725215197</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004713372327387333</v>
+        <v>0.0003753943601623178</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001557739800773561</v>
+        <v>0.0009118799935095012</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002316735684871674</v>
+        <v>0.0005538745899684727</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001577171962708235</v>
+        <v>0.0001236996613442898</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.002690279157832265</v>
+        <v>0.0003157879691570997</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0002194590924773365</v>
+        <v>0.0006257208297029138</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.002883559558540583</v>
+        <v>0.0004216836532577872</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.005363774951547384</v>
+        <v>0.0001805867068469524</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.004029633477330208</v>
+        <v>0.001633794046938419</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0002332301810383797</v>
+        <v>0.0003916864807251841</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0005943025462329388</v>
+        <v>0.0008657372090965509</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.001392165431752801</v>
+        <v>2.088579640258104e-05</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.001168336835689843</v>
+        <v>0.000194428677787073</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0004210535262245685</v>
+        <v>0.001141252694651484</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0002248954551760107</v>
+        <v>0.0008545843884348869</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0004043710068799555</v>
+        <v>0.0004504609969444573</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.006512745283544064</v>
+        <v>0.0005185005720704794</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.004661375656723976</v>
+        <v>0.0007878208416514099</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0005959460977464914</v>
+        <v>0.0003339206450618804</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.002263609319925308</v>
+        <v>2.282474451931193e-05</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.001977189211174846</v>
+        <v>5.149808566784486e-05</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.000608417671173811</v>
+        <v>4.845683361054398e-05</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.01179163064807653</v>
+        <v>0.001970336772501469</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.0005706046940758824</v>
+        <v>0.000637628196272999</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.005139123648405075</v>
+        <v>0.001615515910089016</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.001023468561470509</v>
+        <v>0.002514352323487401</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.0075764125213027</v>
+        <v>0.001618441776372492</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.004285859875380993</v>
+        <v>1.442951906938106e-05</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.006021314766258001</v>
+        <v>0.000260440690908581</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.002278266474604607</v>
+        <v>0.0005265015061013401</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0004080903599970043</v>
+        <v>0.0005932826898060739</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.006425797939300537</v>
+        <v>0.0003688701544888318</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.004954872652888298</v>
+        <v>0.0009641837677918375</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.004342463798820972</v>
+        <v>0.0001860741176642478</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.005017416086047888</v>
+        <v>0.0009194946615025401</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.00505472905933857</v>
+        <v>0.0007361092139035463</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.005535796284675598</v>
+        <v>0.0006987800588831306</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.001971045043319464</v>
+        <v>0.001346347271464765</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.005499374121427536</v>
+        <v>0.0006381792481988668</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.002095826203003526</v>
+        <v>0.0002090664929710329</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.00450443010777235</v>
+        <v>0.0006621296633966267</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.002907013753429055</v>
+        <v>0.0001327132922597229</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.002860247623175383</v>
+        <v>0.0004179467796348035</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.005646249745041132</v>
+        <v>0.0002042835840256885</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.002669682726264</v>
+        <v>0.0001646431483095512</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.0003547421074472368</v>
+        <v>0.0002349540445720777</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.001073990948498249</v>
+        <v>0.0004249995981808752</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.001968359109014273</v>
+        <v>0.0002141228469554335</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.001066792174242437</v>
+        <v>7.925187674118206e-05</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.006617065519094467</v>
+        <v>0.001564701786264777</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.00230915704742074</v>
+        <v>0.0006330724572762847</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.004790401551872492</v>
+        <v>0.001781647093594074</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.003352103289216757</v>
+        <v>9.532734111417085e-05</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.000310928124235943</v>
+        <v>0.0008326561655849218</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.00104459235444665</v>
+        <v>0.0004353255499154329</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.00471058813855052</v>
+        <v>0.000182898817001842</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.001709682634100318</v>
+        <v>0.0001666434982325882</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.0003553801216185093</v>
+        <v>0.0002373958413954824</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.003369228914380074</v>
+        <v>0.001358538866043091</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.001554287038743496</v>
+        <v>0.0001771173265296966</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.002408106811344624</v>
+        <v>0.001180359860882163</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.002008480252698064</v>
+        <v>0.0001039210910676047</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0001896534959087148</v>
+        <v>0.0002362996456213295</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0004125146078877151</v>
+        <v>3.179252234986052e-05</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.0013664027210325</v>
+        <v>0.0001296121336054057</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0007838881574571133</v>
+        <v>6.674094765912741e-05</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.003722716122865677</v>
+        <v>0.0003390201018191874</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0004452423891052604</v>
+        <v>0.0003286322171334177</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.0002078710531350225</v>
+        <v>0.001805235515348613</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.003094956511631608</v>
+        <v>0.002310140989720821</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.001647751778364182</v>
+        <v>0.0007030044216662645</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.001829937682487071</v>
+        <v>0.0005956697859801352</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.003273473819717765</v>
+        <v>0.0004134076007176191</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.00625268742442131</v>
+        <v>0.0005871651228517294</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0005625860649161041</v>
+        <v>2.022954868152738e-05</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.0005300588090904057</v>
+        <v>0.0002399399818386883</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.002688986016437411</v>
+        <v>0.001325708697549999</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.002457620576024055</v>
+        <v>0.0003249775327276438</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.002439534291625023</v>
+        <v>0.0011937360977754</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.00155714200809598</v>
+        <v>0.0001532123278593644</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0006920549203641713</v>
+        <v>0.0003101238689851016</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0005395423504523933</v>
+        <v>1.978116051759571e-05</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.00119104771874845</v>
+        <v>6.796716479584575e-05</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.692944690352306e-05</v>
+        <v>0.0001714451500447467</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.001510612899437547</v>
+        <v>0.0005482651758939028</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.004813096486032009</v>
+        <v>0.0009961389005184174</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.000795047206338495</v>
+        <v>0.0007557190838269889</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.01088720839470625</v>
+        <v>0.001665067509748042</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.001133860554546118</v>
+        <v>0.0007766195340082049</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.002216489054262638</v>
+        <v>0.002769837854430079</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.001626695622690022</v>
+        <v>0.0001393970451317728</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0003230334259569645</v>
+        <v>0.001705737435258925</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0002759982307907194</v>
+        <v>0.0006162460194900632</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.001382412272505462</v>
+        <v>0.0001926742115756497</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.003271130844950676</v>
+        <v>0.0007471648277714849</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.001970718149095774</v>
+        <v>0.0001396296138409525</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.001994813559576869</v>
+        <v>0.0006120278849266469</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.000988739775493741</v>
+        <v>2.937401586677879e-05</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.002687689382582903</v>
+        <v>0.0001860706252045929</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.002997430274263024</v>
+        <v>0.0006709841545671225</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0009468060452491045</v>
+        <v>0.0002496160450391471</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.0002100292476825416</v>
+        <v>0.001345535041764379</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0002956416283268481</v>
+        <v>8.417412027483806e-05</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.000898388447239995</v>
+        <v>0.0003997803141828626</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.001090151374228299</v>
+        <v>0.000555241946130991</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.000902289233636111</v>
+        <v>0.0002226284996140748</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.001584411365911365</v>
+        <v>0.0001730197545839474</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.002477034693583846</v>
+        <v>0.0008768306579440832</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0003250651934649795</v>
+        <v>5.629808947560377e-05</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.002297797007486224</v>
+        <v>0.00221042544580996</v>
       </c>
       <c r="EE5" t="n">
-        <v>1.046364195644855e-05</v>
+        <v>0.001763945096172392</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0001806957880035043</v>
+        <v>0.0007944540702737868</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.001841213554143906</v>
+        <v>0.0009740270907059312</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.001660183421336114</v>
+        <v>0.0005782692460343242</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.002011066069826484</v>
+        <v>0.00153530272655189</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.003919358365237713</v>
+        <v>0.00016510792193003</v>
       </c>
       <c r="EK5" t="n">
-        <v>5.291432898957282e-05</v>
+        <v>3.391302016098052e-06</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.00205964082852006</v>
+        <v>0.0001102600581361912</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.0006027686758898199</v>
+        <v>0.0003690684679895639</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.0004984121187590063</v>
+        <v>0.0001339728478342295</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.001031357212923467</v>
+        <v>0.0001466035755584016</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.001726797549054027</v>
+        <v>0.001533663715235889</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.002200254006311297</v>
+        <v>0.0001956849591806531</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.000700834090821445</v>
+        <v>0.0003167382092215121</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.001655518310144544</v>
+        <v>0.0001543651014799252</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.003344691824167967</v>
+        <v>0.0001201710110763088</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.002573950216174126</v>
+        <v>0.0004294777754694223</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.001287249848246574</v>
+        <v>0.000256777711911127</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.001510170521214604</v>
+        <v>0.0008290527039207518</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.0002783239469863474</v>
+        <v>0.0001912008883664384</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.002414316637441516</v>
+        <v>0.001359399291686714</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.001583598554134369</v>
+        <v>0.0002249353565275669</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.002689511282369494</v>
+        <v>0.001412313780747354</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.002332476200535893</v>
+        <v>1.624148535483982e-05</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0003327534650452435</v>
+        <v>0.0002368250134168193</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0007735403487458825</v>
+        <v>0.0001016097739920951</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.001714664627797902</v>
+        <v>0.0001403065689373761</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.0008420048980042338</v>
+        <v>0.0002609050716273487</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0008426851709373295</v>
+        <v>1.217643148265779e-05</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.002036634832620621</v>
+        <v>0.0008339742198586464</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.0005370122962631285</v>
+        <v>0.0001713009260129184</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.001903116470202804</v>
+        <v>0.0008451102767139673</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.002086918335407972</v>
+        <v>0.0002076731179840863</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.000902318861335516</v>
+        <v>5.015426722820848e-05</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0003240532241761684</v>
+        <v>0.0003711573081091046</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.001745852408930659</v>
+        <v>0.0006701945094391704</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.001597653026692569</v>
+        <v>0.0006116926670074463</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.00306848855689168</v>
+        <v>0.0006721355603076518</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.001060352427884936</v>
+        <v>0.001795191783457994</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.001562780002132058</v>
+        <v>0.0006133518181741238</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.001200843718834221</v>
+        <v>0.0009820830309763551</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.007657501380890608</v>
+        <v>0.00135551649145782</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.002615624340251088</v>
+        <v>0.001235693809576333</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0002371252048760653</v>
+        <v>0.0001713528763502836</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.0004619216779246926</v>
+        <v>0.0006879987777210772</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.002280463464558125</v>
+        <v>0.001606492092832923</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.002524733077734709</v>
+        <v>0.000392485992051661</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0002647777437232435</v>
+        <v>0.0002737873583100736</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.0007551744347438216</v>
+        <v>0.0002876380167435855</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.001512054586783051</v>
+        <v>0.001034507993608713</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.002367714187130332</v>
+        <v>0.0001633347710594535</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.005552985705435276</v>
+        <v>0.0004634808283299208</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.005258283577859402</v>
+        <v>0.0007385571952909231</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.0003939290763810277</v>
+        <v>0.000257141247857362</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.002618982689455152</v>
+        <v>0.0005275806179270148</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.000457492598798126</v>
+        <v>2.044805713641296e-10</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0004355424316599965</v>
+        <v>4.912317774774522e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0002151189837604761</v>
+        <v>2.290583833719495e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000335206714225933</v>
+        <v>1.9720231003717e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0006194452289491892</v>
+        <v>5.433022365330942e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0004834791179746389</v>
+        <v>1.203097399482544e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0002182298339903355</v>
+        <v>1.060220133908274e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0002221458271378651</v>
+        <v>1.178591335637691e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0006931590614840388</v>
+        <v>1.820158745946543e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002315977762918919</v>
+        <v>3.009428817257742e-11</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0004241572751197964</v>
+        <v>4.790673968635417e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0003903521865140647</v>
+        <v>3.443348384202238e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>6.030604708939791e-07</v>
+        <v>8.367879167359149e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001517977216280997</v>
+        <v>3.09509862184143e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001061453513102606</v>
+        <v>1.467981736169577e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0002007036237046123</v>
+        <v>1.732562426859374e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0006101515609771013</v>
+        <v>1.197225651949907e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>2.238020533695817e-05</v>
+        <v>1.601417609631284e-11</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001714971731416881</v>
+        <v>1.146295385001661e-11</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0007140092202462256</v>
+        <v>5.275239689517264e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001240184355992824</v>
+        <v>2.603793569644353e-11</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0002970545901916921</v>
+        <v>4.428257760480392e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001528670080006123</v>
+        <v>6.922021844602e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>0.000267134775640443</v>
+        <v>6.501414684390028e-11</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001905178360175341</v>
+        <v>3.21968895988789e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0006537102744914591</v>
+        <v>9.488788643707835e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.158917348220712e-05</v>
+        <v>2.236854729220639e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.51588610606268e-05</v>
+        <v>1.147072645202307e-10</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.292436202988029e-05</v>
+        <v>3.426800232464444e-10</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0003958843881264329</v>
+        <v>3.892076244627063e-11</v>
       </c>
       <c r="AE6" t="n">
-        <v>4.861279739998281e-05</v>
+        <v>1.100043112156612e-10</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0005609682411886752</v>
+        <v>4.657559338205886e-10</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.000163461416377686</v>
+        <v>3.815159577147398e-10</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0008189745130948722</v>
+        <v>3.616953958562874e-10</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0002876456128433347</v>
+        <v>3.270192727722332e-10</v>
       </c>
       <c r="AJ6" t="n">
-        <v>4.739534779218957e-05</v>
+        <v>3.623776279049196e-11</v>
       </c>
       <c r="AK6" t="n">
-        <v>9.047881758306175e-05</v>
+        <v>2.267138005107583e-10</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0002392160968156531</v>
+        <v>3.366032452767342e-10</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0001093148966901936</v>
+        <v>6.731972618245763e-11</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0006917444989085197</v>
+        <v>3.267694725916925e-10</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.0004162726108916104</v>
+        <v>2.382568864423007e-10</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.577073195832781e-05</v>
+        <v>2.690889872036806e-11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.0001519857905805111</v>
+        <v>2.852229563643505e-11</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.0001430057018296793</v>
+        <v>3.510802759620901e-12</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.431148408912122e-05</v>
+        <v>3.502786671827351e-10</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.0008323481888510287</v>
+        <v>2.001489807224033e-10</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.0003575633454602212</v>
+        <v>9.036972836717894e-10</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.0001180691397166811</v>
+        <v>1.789378228922445e-10</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.001042040414176881</v>
+        <v>2.870544912880746e-10</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.001635184395126998</v>
+        <v>8.728850975359137e-11</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.000674436567351222</v>
+        <v>7.826862491455699e-10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.001446529407985508</v>
+        <v>5.190596841231354e-10</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.001480686129070818</v>
+        <v>7.073517327427226e-10</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.000696174509357661</v>
+        <v>2.495171014249564e-10</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.0007775240810588002</v>
+        <v>2.850432112566637e-10</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0002671282854862511</v>
+        <v>7.781404409712422e-10</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.074380507925525e-05</v>
+        <v>1.773151903083914e-10</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.224043318070471e-05</v>
+        <v>7.327860540584652e-10</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.0004163476405665278</v>
+        <v>4.038767653646858e-10</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.000314077886287123</v>
+        <v>1.895744811131195e-10</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0008005250128917396</v>
+        <v>5.650867551665328e-10</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0005131036159582436</v>
+        <v>1.066825405793281e-09</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.0004710405482910573</v>
+        <v>3.070709519992221e-10</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.0003220424405299127</v>
+        <v>1.828410062243435e-10</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0001622476120246574</v>
+        <v>2.0437453118749e-10</v>
       </c>
       <c r="BN6" t="n">
-        <v>3.690774610731751e-05</v>
+        <v>2.297795287375948e-10</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.001618735026568174</v>
+        <v>2.753876016114987e-10</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0003451187803875655</v>
+        <v>1.382974984531771e-11</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0002327538095414639</v>
+        <v>1.002263272376069e-10</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0002572771045379341</v>
+        <v>3.297949968672498e-10</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.0008131685899570584</v>
+        <v>2.796238796065609e-10</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.0006420453428290784</v>
+        <v>3.063125586511006e-10</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.0002955388627015054</v>
+        <v>2.215416600170883e-10</v>
       </c>
       <c r="BV6" t="n">
-        <v>9.625015809433535e-05</v>
+        <v>1.050205339359067e-10</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.0002212614199379459</v>
+        <v>4.067515768646501e-11</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.0003120955661870539</v>
+        <v>9.144129897720177e-10</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0005798318306915462</v>
+        <v>7.981970640003055e-10</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.0002013846242334694</v>
+        <v>4.844205037102256e-10</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.0007806912763044238</v>
+        <v>2.175636060197661e-10</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.0008010721649043262</v>
+        <v>2.22673504635118e-10</v>
       </c>
       <c r="CC6" t="n">
-        <v>1.878250986919738e-05</v>
+        <v>4.143855258931239e-10</v>
       </c>
       <c r="CD6" t="n">
-        <v>1.580421667313203e-05</v>
+        <v>3.177749036131772e-11</v>
       </c>
       <c r="CE6" t="n">
-        <v>2.325187051610555e-05</v>
+        <v>1.45356643388439e-12</v>
       </c>
       <c r="CF6" t="n">
-        <v>4.599978274200112e-05</v>
+        <v>1.178833142212454e-10</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.000260324974078685</v>
+        <v>1.346035921612199e-10</v>
       </c>
       <c r="CH6" t="n">
-        <v>6.465206388384104e-05</v>
+        <v>9.212113016854317e-11</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.110217428707983e-05</v>
+        <v>3.374337753658807e-10</v>
       </c>
       <c r="CJ6" t="n">
-        <v>9.553368727210909e-05</v>
+        <v>2.285012179470414e-10</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.0001069513236870989</v>
+        <v>2.418378344803962e-11</v>
       </c>
       <c r="CL6" t="n">
-        <v>7.563787221442908e-05</v>
+        <v>2.443023006115652e-10</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.0002037046506302431</v>
+        <v>2.331962678514543e-10</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0004732106754090637</v>
+        <v>3.028614303790533e-10</v>
       </c>
       <c r="CO6" t="n">
-        <v>4.516758053796366e-06</v>
+        <v>1.724879961084724e-11</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.0003951807739213109</v>
+        <v>2.65710953240017e-10</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0006455162074416876</v>
+        <v>8.87143802863477e-10</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.0003804976586252451</v>
+        <v>1.626834916779174e-10</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.0007168682059273124</v>
+        <v>1.144883077230929e-09</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.0004101857193745673</v>
+        <v>4.816918530714531e-10</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.0008368171402253211</v>
+        <v>1.417619077681564e-10</v>
       </c>
       <c r="CV6" t="n">
-        <v>7.554150943178684e-05</v>
+        <v>6.422619380774819e-11</v>
       </c>
       <c r="CW6" t="n">
-        <v>4.093260577064939e-05</v>
+        <v>2.62911289961032e-11</v>
       </c>
       <c r="CX6" t="n">
-        <v>2.186709389206953e-05</v>
+        <v>7.153044823127175e-11</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.0002953998045995831</v>
+        <v>1.849666669828665e-10</v>
       </c>
       <c r="CZ6" t="n">
-        <v>6.179789124871604e-06</v>
+        <v>1.231910129462221e-10</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.0001558840449433774</v>
+        <v>3.833777462158849e-10</v>
       </c>
       <c r="DB6" t="n">
-        <v>2.779733040370047e-05</v>
+        <v>2.532558607271085e-10</v>
       </c>
       <c r="DC6" t="n">
-        <v>9.797974780667573e-05</v>
+        <v>7.026719484048982e-12</v>
       </c>
       <c r="DD6" t="n">
-        <v>6.811581260990351e-05</v>
+        <v>2.587173530965714e-10</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.0007830740651115775</v>
+        <v>5.766738198076382e-10</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.001180441351607442</v>
+        <v>1.124158877097159e-09</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.019513365463354e-05</v>
+        <v>4.757719773706981e-10</v>
       </c>
       <c r="DH6" t="n">
-        <v>2.645642962306738e-05</v>
+        <v>2.834550094643618e-10</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0007934045279398561</v>
+        <v>5.70984814984854e-10</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.001134891994297504</v>
+        <v>7.116323641476185e-10</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.000179704831680283</v>
+        <v>6.332581681256499e-11</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.0004855737497564405</v>
+        <v>7.990036410276957e-11</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.000977651565335691</v>
+        <v>1.063018284508388e-10</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.0002103850129060447</v>
+        <v>4.374783868499321e-10</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.0002552149817347527</v>
+        <v>1.354580614343348e-10</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.0002000596723519266</v>
+        <v>2.340216909146875e-10</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.0001033266162266955</v>
+        <v>1.14553144747731e-09</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.0008562749717384577</v>
+        <v>3.420804750575712e-10</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.0002177402639063075</v>
+        <v>6.70717509310137e-11</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.0004779441806022078</v>
+        <v>4.283828569651149e-10</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.0002996824914589524</v>
+        <v>2.395664500109973e-10</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.0004651099734473974</v>
+        <v>8.192316269806099e-11</v>
       </c>
       <c r="DW6" t="n">
-        <v>4.389067180454731e-05</v>
+        <v>2.811988975004454e-10</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.0001830788241932169</v>
+        <v>3.512427848573196e-10</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.0002255832368973643</v>
+        <v>1.114782294253658e-10</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.000618250051047653</v>
+        <v>5.94875537718309e-10</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.0006559378816746175</v>
+        <v>1.510574720864355e-10</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0004859266337007284</v>
+        <v>2.24539137283486e-10</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.0001604160788701847</v>
+        <v>1.786589903796099e-10</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.0004618771490640938</v>
+        <v>4.231541228527647e-10</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.0003280425153207034</v>
+        <v>1.481355316190758e-11</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.0003370853664819151</v>
+        <v>3.917892676952306e-10</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.000539719476364553</v>
+        <v>8.048680472105829e-11</v>
       </c>
       <c r="EH6" t="n">
-        <v>2.51892033702461e-05</v>
+        <v>1.328646914711129e-11</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.001266757375560701</v>
+        <v>7.121952472211035e-10</v>
       </c>
       <c r="EJ6" t="n">
-        <v>2.344011227251031e-05</v>
+        <v>3.604467280204915e-10</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.0005699970643036067</v>
+        <v>2.895970130367687e-10</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.0001783152692951262</v>
+        <v>1.156075166153236e-10</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.0003775461227633059</v>
+        <v>1.564463419923001e-10</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.0002253862621728331</v>
+        <v>5.298944061316035e-10</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.000101854486274533</v>
+        <v>2.418708289209093e-10</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.0001411577395629138</v>
+        <v>1.716227854275942e-10</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.0001217457902384922</v>
+        <v>1.521632958523256e-10</v>
       </c>
       <c r="ER6" t="n">
-        <v>6.625382957281545e-05</v>
+        <v>2.124532494374165e-10</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.0002477543312124908</v>
+        <v>8.658657124627211e-10</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.0005504541913978755</v>
+        <v>2.367933626956642e-10</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.0005429849261417985</v>
+        <v>2.803035581422364e-12</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.0005150189972482622</v>
+        <v>5.070395492356994e-12</v>
       </c>
       <c r="EW6" t="n">
-        <v>3.856602415908128e-05</v>
+        <v>3.79452892718124e-11</v>
       </c>
       <c r="EX6" t="n">
-        <v>1.066990080289543e-06</v>
+        <v>3.760602940161561e-12</v>
       </c>
       <c r="EY6" t="n">
-        <v>2.748584665823728e-05</v>
+        <v>1.3307792368078e-12</v>
       </c>
       <c r="EZ6" t="n">
-        <v>7.214357174234465e-05</v>
+        <v>8.174454863008052e-11</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.0003143431385979056</v>
+        <v>1.218772166522442e-10</v>
       </c>
       <c r="FB6" t="n">
-        <v>3.07464724755846e-05</v>
+        <v>7.791622902431072e-11</v>
       </c>
       <c r="FC6" t="n">
-        <v>7.77044115238823e-05</v>
+        <v>3.350119348599634e-10</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.0001469948620069772</v>
+        <v>2.63256527688327e-10</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.0002426058927085251</v>
+        <v>4.867500846827966e-11</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.0001622175914235413</v>
+        <v>1.795246312719101e-10</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.0004240804119035602</v>
+        <v>6.780042083320836e-10</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.0001331077219219878</v>
+        <v>1.77902428899479e-10</v>
       </c>
       <c r="FI6" t="n">
-        <v>5.657269139192067e-05</v>
+        <v>2.027355366918115e-10</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.000903139531146735</v>
+        <v>1.317997655458925e-10</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.0002238741144537926</v>
+        <v>1.548242090088081e-10</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.0008063296554610133</v>
+        <v>1.02569980287015e-10</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.0003609771956689656</v>
+        <v>9.905305742297088e-11</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.0001172717893496156</v>
+        <v>4.468767023091402e-10</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.0002769660786725581</v>
+        <v>7.095721232808216e-11</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.0002840209344867617</v>
+        <v>4.097168437855458e-11</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.0001856415619840845</v>
+        <v>1.338572364062429e-09</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.0002943917061202228</v>
+        <v>7.047924466263567e-10</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.0004792660183738917</v>
+        <v>3.099027978681335e-10</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.002362665720283985</v>
+        <v>8.860808753397009e-10</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.001068817917257547</v>
+        <v>4.421016885913787e-10</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.0007176029030233622</v>
+        <v>1.165104235312242e-09</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.0004737996205221862</v>
+        <v>2.606969640162049e-10</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.0001391524565406144</v>
+        <v>7.352781578040535e-12</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.0003004281024914235</v>
+        <v>1.632155244291056e-10</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.0005441035609692335</v>
+        <v>1.180548540868909e-11</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.0002713579451665282</v>
+        <v>3.775933732352854e-11</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.001035231398418546</v>
+        <v>5.774976052919101e-10</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.0004295601975172758</v>
+        <v>3.233404377578353e-10</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.0006609845440834761</v>
+        <v>5.611188735876738e-10</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.0005110930651426315</v>
+        <v>2.4341102050629e-11</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.001311778672970831</v>
+        <v>5.361266430803369e-10</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.000865842099301517</v>
+        <v>1.180059244765275e-10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.124781738326419e-05</v>
+        <v>4.610215001096298e-14</v>
       </c>
       <c r="B7" t="n">
-        <v>6.281507376115769e-05</v>
+        <v>9.469001646146558e-15</v>
       </c>
       <c r="C7" t="n">
-        <v>9.292032700614072e-06</v>
+        <v>1.827752223659482e-13</v>
       </c>
       <c r="D7" t="n">
-        <v>1.456132304156199e-05</v>
+        <v>1.610909349707493e-13</v>
       </c>
       <c r="E7" t="n">
-        <v>5.354003587854095e-05</v>
+        <v>1.362752142033963e-13</v>
       </c>
       <c r="F7" t="n">
-        <v>2.01443544938229e-05</v>
+        <v>4.485796770929001e-13</v>
       </c>
       <c r="G7" t="n">
-        <v>3.264729821239598e-05</v>
+        <v>1.623700495887934e-14</v>
       </c>
       <c r="H7" t="n">
-        <v>1.552728099341039e-05</v>
+        <v>8.50514727005966e-14</v>
       </c>
       <c r="I7" t="n">
-        <v>4.700244244304486e-05</v>
+        <v>3.354531550540246e-13</v>
       </c>
       <c r="J7" t="n">
-        <v>1.216173586726654e-05</v>
+        <v>4.117805272110808e-14</v>
       </c>
       <c r="K7" t="n">
-        <v>3.041170202777721e-05</v>
+        <v>3.092750664943078e-13</v>
       </c>
       <c r="L7" t="n">
-        <v>1.477768819313496e-05</v>
+        <v>1.67548537977763e-13</v>
       </c>
       <c r="M7" t="n">
-        <v>4.028710827697068e-05</v>
+        <v>3.382420211972548e-13</v>
       </c>
       <c r="N7" t="n">
-        <v>8.75599798746407e-05</v>
+        <v>8.718543329780046e-14</v>
       </c>
       <c r="O7" t="n">
-        <v>6.133417173259659e-06</v>
+        <v>4.112873236428172e-13</v>
       </c>
       <c r="P7" t="n">
-        <v>1.395631625200622e-05</v>
+        <v>9.004622947891144e-14</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.40283804689534e-07</v>
+        <v>8.449066912687847e-14</v>
       </c>
       <c r="R7" t="n">
-        <v>3.995164297521114e-05</v>
+        <v>2.170566786204031e-13</v>
       </c>
       <c r="S7" t="n">
-        <v>6.084949291107478e-07</v>
+        <v>9.526135034878397e-14</v>
       </c>
       <c r="T7" t="n">
-        <v>1.458392580389045e-05</v>
+        <v>1.865369566710767e-13</v>
       </c>
       <c r="U7" t="n">
-        <v>1.163641718449071e-05</v>
+        <v>7.785573807829113e-14</v>
       </c>
       <c r="V7" t="n">
-        <v>7.856078809709288e-07</v>
+        <v>1.948139186861569e-13</v>
       </c>
       <c r="W7" t="n">
-        <v>2.710330227273516e-05</v>
+        <v>3.635256971747797e-13</v>
       </c>
       <c r="X7" t="n">
-        <v>1.622697709535714e-08</v>
+        <v>1.552880138930637e-13</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.94875451597909e-06</v>
+        <v>5.209173343330084e-14</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.705522481643129e-05</v>
+        <v>9.407384403805133e-14</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.506771231011953e-06</v>
+        <v>6.306809458359042e-14</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.174979378352873e-08</v>
+        <v>8.22384966115558e-14</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.426118953735568e-05</v>
+        <v>7.515234772383431e-14</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.657004708657041e-05</v>
+        <v>1.129007504889826e-13</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.757786205620505e-05</v>
+        <v>2.631653575613235e-13</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.578284172865096e-05</v>
+        <v>2.378506971185881e-14</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.297605508123524e-05</v>
+        <v>1.443747600854764e-13</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.77398896489467e-06</v>
+        <v>6.971067603375736e-14</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.446920578018762e-06</v>
+        <v>2.080258301772123e-13</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.618241342133842e-05</v>
+        <v>4.387778050510098e-14</v>
       </c>
       <c r="AK7" t="n">
-        <v>8.70551957632415e-06</v>
+        <v>1.312380515676101e-13</v>
       </c>
       <c r="AL7" t="n">
-        <v>8.690243703313172e-06</v>
+        <v>7.053370067915468e-14</v>
       </c>
       <c r="AM7" t="n">
-        <v>4.117273874726379e-06</v>
+        <v>4.783161171827144e-14</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.499808488209965e-06</v>
+        <v>2.477824260875561e-13</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.130303280660883e-05</v>
+        <v>9.952493473450175e-14</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.011838089150842e-05</v>
+        <v>2.186777675443081e-14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.817041245696601e-06</v>
+        <v>5.568109992179493e-15</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.047910857072566e-05</v>
+        <v>5.735647688135531e-14</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.436732398171443e-06</v>
+        <v>6.853009506440147e-14</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.920747647294775e-06</v>
+        <v>2.842271570554535e-14</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.697716551367193e-05</v>
+        <v>5.065077047020083e-13</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.391179689060664e-06</v>
+        <v>6.145422576852785e-14</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.484540891600773e-05</v>
+        <v>9.739627995167949e-14</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.177053440595046e-05</v>
+        <v>1.094324148442558e-13</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.320262087276205e-05</v>
+        <v>1.973422781523931e-14</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.423818684997968e-05</v>
+        <v>6.018902281960947e-14</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.085370942950249e-05</v>
+        <v>1.128700269099198e-13</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.281838922295719e-05</v>
+        <v>7.841715829199486e-14</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.507759001626255e-07</v>
+        <v>1.032675870813946e-13</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.51366966747446e-05</v>
+        <v>1.264029164541394e-13</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.533277433438343e-07</v>
+        <v>3.189659772201078e-14</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.198405804345384e-05</v>
+        <v>1.401393514037161e-13</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.892873064614832e-05</v>
+        <v>7.540680319745308e-15</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.965738404891454e-06</v>
+        <v>2.209652410047405e-13</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.424619196972344e-06</v>
+        <v>9.151265357477956e-14</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1.422938339601387e-06</v>
+        <v>1.550763911815217e-13</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.853562470292673e-05</v>
+        <v>1.232110388108693e-13</v>
       </c>
       <c r="BL7" t="n">
-        <v>9.987398698285688e-06</v>
+        <v>1.325527686744932e-13</v>
       </c>
       <c r="BM7" t="n">
-        <v>4.723415258922614e-06</v>
+        <v>1.699099574144908e-13</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.988910298678093e-05</v>
+        <v>9.146731867737661e-15</v>
       </c>
       <c r="BO7" t="n">
-        <v>6.526501238113269e-06</v>
+        <v>2.581594131718414e-14</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.752250970341265e-05</v>
+        <v>1.998583319239716e-13</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.805768260965124e-05</v>
+        <v>1.716110570705934e-13</v>
       </c>
       <c r="BR7" t="n">
-        <v>1.024055563902948e-05</v>
+        <v>2.274694376001168e-13</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.002187218546169e-06</v>
+        <v>3.054905639435571e-14</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.276870069792494e-06</v>
+        <v>3.664277404722902e-14</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.155183776470949e-06</v>
+        <v>2.267463154086505e-14</v>
       </c>
       <c r="BV7" t="n">
-        <v>3.71235073544085e-05</v>
+        <v>8.641361009999876e-14</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.616190274944529e-05</v>
+        <v>1.277514606688041e-13</v>
       </c>
       <c r="BX7" t="n">
-        <v>2.655197704370948e-06</v>
+        <v>2.286994649648016e-13</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.753728591022082e-06</v>
+        <v>2.188353664944742e-13</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.43365332405665e-05</v>
+        <v>2.025220675839698e-13</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.463521013851278e-06</v>
+        <v>3.087620762363963e-14</v>
       </c>
       <c r="CB7" t="n">
-        <v>6.902695076860255e-06</v>
+        <v>1.463684181452971e-13</v>
       </c>
       <c r="CC7" t="n">
-        <v>1.28954925457947e-05</v>
+        <v>1.739001195648349e-13</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.353398033643316e-06</v>
+        <v>3.97304056516147e-14</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.342829636996612e-05</v>
+        <v>2.083607029588434e-15</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.300579126313096e-06</v>
+        <v>2.32948443114377e-14</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.311693378942437e-06</v>
+        <v>7.855528564876951e-14</v>
       </c>
       <c r="CH7" t="n">
-        <v>9.381278687214945e-06</v>
+        <v>9.03460672837782e-15</v>
       </c>
       <c r="CI7" t="n">
-        <v>4.1459093154117e-06</v>
+        <v>8.044338985083513e-14</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.928398205564008e-07</v>
+        <v>3.467884345572519e-14</v>
       </c>
       <c r="CK7" t="n">
-        <v>5.647674697684124e-06</v>
+        <v>4.313300137523922e-14</v>
       </c>
       <c r="CL7" t="n">
-        <v>9.192674951918889e-06</v>
+        <v>8.477414733740196e-14</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.449471983505646e-05</v>
+        <v>7.018304259151856e-14</v>
       </c>
       <c r="CN7" t="n">
-        <v>6.656298864982091e-06</v>
+        <v>2.571031495340881e-13</v>
       </c>
       <c r="CO7" t="n">
-        <v>2.987996595038567e-06</v>
+        <v>1.015506445210465e-13</v>
       </c>
       <c r="CP7" t="n">
-        <v>9.413576663064305e-06</v>
+        <v>2.134621960529076e-14</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.969192039221525e-05</v>
+        <v>8.271963843065055e-14</v>
       </c>
       <c r="CR7" t="n">
-        <v>9.614552254788578e-06</v>
+        <v>1.336363542069931e-14</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.36664124915842e-05</v>
+        <v>6.178015727036773e-14</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.257550477224868e-05</v>
+        <v>5.358070215809307e-14</v>
       </c>
       <c r="CU7" t="n">
-        <v>3.013266223206301e-06</v>
+        <v>9.58630283444048e-14</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.325609358422298e-07</v>
+        <v>6.167652109520527e-14</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.660258567426354e-05</v>
+        <v>3.385675393470164e-16</v>
       </c>
       <c r="CX7" t="n">
-        <v>9.714244697534014e-08</v>
+        <v>1.467134248291091e-14</v>
       </c>
       <c r="CY7" t="n">
-        <v>3.67537950296537e-07</v>
+        <v>8.894533059296966e-14</v>
       </c>
       <c r="CZ7" t="n">
-        <v>8.259035894297995e-06</v>
+        <v>1.166760102162129e-14</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.541079311413341e-06</v>
+        <v>7.905953452666536e-14</v>
       </c>
       <c r="DB7" t="n">
-        <v>2.871308197427425e-06</v>
+        <v>1.174447095565051e-14</v>
       </c>
       <c r="DC7" t="n">
-        <v>7.535021723015234e-06</v>
+        <v>2.013118472377236e-14</v>
       </c>
       <c r="DD7" t="n">
-        <v>8.137851637002314e-07</v>
+        <v>7.560167498543019e-14</v>
       </c>
       <c r="DE7" t="n">
-        <v>2.737266186159104e-06</v>
+        <v>8.393185777465229e-14</v>
       </c>
       <c r="DF7" t="n">
-        <v>4.927436384605244e-05</v>
+        <v>9.142923099387038e-14</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.007262810366228e-05</v>
+        <v>1.248310130394156e-13</v>
       </c>
       <c r="DH7" t="n">
-        <v>2.41134603129467e-05</v>
+        <v>2.293827562789563e-14</v>
       </c>
       <c r="DI7" t="n">
-        <v>3.433859819779173e-05</v>
+        <v>2.445606041355346e-14</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.6960809918819e-05</v>
+        <v>1.356647812752326e-13</v>
       </c>
       <c r="DK7" t="n">
-        <v>1.584892197570298e-05</v>
+        <v>6.839364144473059e-14</v>
       </c>
       <c r="DL7" t="n">
-        <v>3.73992879758589e-05</v>
+        <v>9.257251540849276e-14</v>
       </c>
       <c r="DM7" t="n">
-        <v>8.937521670304704e-06</v>
+        <v>2.946114421756123e-14</v>
       </c>
       <c r="DN7" t="n">
-        <v>5.765974037785782e-06</v>
+        <v>2.824817440236823e-14</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.107744810724398e-05</v>
+        <v>7.102103600315976e-15</v>
       </c>
       <c r="DP7" t="n">
-        <v>4.616457772499416e-06</v>
+        <v>4.395421675826121e-14</v>
       </c>
       <c r="DQ7" t="n">
-        <v>4.960702426615171e-06</v>
+        <v>2.060703902439717e-13</v>
       </c>
       <c r="DR7" t="n">
-        <v>2.862332166841952e-07</v>
+        <v>7.854784531136083e-14</v>
       </c>
       <c r="DS7" t="n">
-        <v>3.707459200086305e-06</v>
+        <v>1.732849568046937e-13</v>
       </c>
       <c r="DT7" t="n">
-        <v>1.877961949503515e-05</v>
+        <v>1.190065569960791e-13</v>
       </c>
       <c r="DU7" t="n">
-        <v>4.180876203463413e-06</v>
+        <v>6.30561005970573e-14</v>
       </c>
       <c r="DV7" t="n">
-        <v>6.026260052749421e-06</v>
+        <v>2.078647990495439e-14</v>
       </c>
       <c r="DW7" t="n">
-        <v>5.439585493149934e-06</v>
+        <v>8.832405564308116e-14</v>
       </c>
       <c r="DX7" t="n">
-        <v>2.983105787279783e-06</v>
+        <v>2.629450815611924e-14</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.464779289672151e-07</v>
+        <v>3.194369275387812e-14</v>
       </c>
       <c r="DZ7" t="n">
-        <v>7.559973255411023e-06</v>
+        <v>7.281593269970951e-14</v>
       </c>
       <c r="EA7" t="n">
-        <v>1.933276507770643e-05</v>
+        <v>3.61970653103838e-14</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.287125996896066e-06</v>
+        <v>5.077060598107294e-14</v>
       </c>
       <c r="EC7" t="n">
-        <v>7.426625415973831e-06</v>
+        <v>1.318668617225974e-13</v>
       </c>
       <c r="ED7" t="n">
-        <v>1.680926652625203e-05</v>
+        <v>5.186194355910612e-14</v>
       </c>
       <c r="EE7" t="n">
-        <v>2.647491237439681e-05</v>
+        <v>4.201382690642748e-14</v>
       </c>
       <c r="EF7" t="n">
-        <v>1.147641341958661e-07</v>
+        <v>2.25067631632464e-14</v>
       </c>
       <c r="EG7" t="n">
-        <v>1.047583282343112e-07</v>
+        <v>4.929470866872274e-14</v>
       </c>
       <c r="EH7" t="n">
-        <v>8.202796379919164e-06</v>
+        <v>6.195917937783582e-14</v>
       </c>
       <c r="EI7" t="n">
-        <v>2.008322098845383e-06</v>
+        <v>1.527483651717065e-13</v>
       </c>
       <c r="EJ7" t="n">
-        <v>1.417674775439082e-05</v>
+        <v>3.60210383114172e-14</v>
       </c>
       <c r="EK7" t="n">
-        <v>2.320281510037603e-06</v>
+        <v>6.440151417794887e-14</v>
       </c>
       <c r="EL7" t="n">
-        <v>1.904463260871125e-06</v>
+        <v>2.722703383280581e-14</v>
       </c>
       <c r="EM7" t="n">
-        <v>1.674170925980434e-05</v>
+        <v>7.516785181490085e-14</v>
       </c>
       <c r="EN7" t="n">
-        <v>9.116563887801021e-06</v>
+        <v>8.935622288755093e-14</v>
       </c>
       <c r="EO7" t="n">
-        <v>4.824208190257195e-06</v>
+        <v>5.418240048250464e-14</v>
       </c>
       <c r="EP7" t="n">
-        <v>2.595521800685674e-05</v>
+        <v>1.613087376346745e-13</v>
       </c>
       <c r="EQ7" t="n">
-        <v>3.314760306238895e-07</v>
+        <v>1.603148223981027e-13</v>
       </c>
       <c r="ER7" t="n">
-        <v>1.082351172954077e-05</v>
+        <v>1.936795044005582e-14</v>
       </c>
       <c r="ES7" t="n">
-        <v>1.468901700718561e-06</v>
+        <v>2.244204984607617e-14</v>
       </c>
       <c r="ET7" t="n">
-        <v>9.868294910120312e-06</v>
+        <v>1.102239366402788e-13</v>
       </c>
       <c r="EU7" t="n">
-        <v>7.399395144602749e-06</v>
+        <v>1.205499729987208e-13</v>
       </c>
       <c r="EV7" t="n">
-        <v>7.101156825228827e-06</v>
+        <v>1.002697951795264e-13</v>
       </c>
       <c r="EW7" t="n">
-        <v>1.864214169700062e-07</v>
+        <v>6.241219292681816e-14</v>
       </c>
       <c r="EX7" t="n">
-        <v>2.274253120049252e-06</v>
+        <v>8.804641857176193e-14</v>
       </c>
       <c r="EY7" t="n">
-        <v>1.635035732761025e-05</v>
+        <v>2.489539268637174e-14</v>
       </c>
       <c r="EZ7" t="n">
-        <v>5.472203611134319e-06</v>
+        <v>4.471357163107932e-14</v>
       </c>
       <c r="FA7" t="n">
-        <v>1.668655158937327e-06</v>
+        <v>7.769250466495986e-14</v>
       </c>
       <c r="FB7" t="n">
-        <v>3.646237473731162e-06</v>
+        <v>3.720583326968568e-15</v>
       </c>
       <c r="FC7" t="n">
-        <v>2.034447334153811e-06</v>
+        <v>8.797663660943533e-14</v>
       </c>
       <c r="FD7" t="n">
-        <v>1.753811829985352e-06</v>
+        <v>4.691014151561243e-14</v>
       </c>
       <c r="FE7" t="n">
-        <v>6.932644282642286e-06</v>
+        <v>3.271960542674916e-14</v>
       </c>
       <c r="FF7" t="n">
-        <v>4.68499251837784e-07</v>
+        <v>8.827479898313242e-14</v>
       </c>
       <c r="FG7" t="n">
-        <v>2.662923179741483e-06</v>
+        <v>2.333502586038955e-13</v>
       </c>
       <c r="FH7" t="n">
-        <v>6.020346518198494e-06</v>
+        <v>8.291423239182097e-14</v>
       </c>
       <c r="FI7" t="n">
-        <v>5.855963536305353e-07</v>
+        <v>9.768048322240583e-14</v>
       </c>
       <c r="FJ7" t="n">
-        <v>6.647651389357634e-06</v>
+        <v>7.158845321013005e-14</v>
       </c>
       <c r="FK7" t="n">
-        <v>1.888305814645719e-05</v>
+        <v>2.761602185537108e-14</v>
       </c>
       <c r="FL7" t="n">
-        <v>2.152576053049415e-05</v>
+        <v>1.365299475038217e-13</v>
       </c>
       <c r="FM7" t="n">
-        <v>6.539085916301701e-06</v>
+        <v>1.57740140394047e-13</v>
       </c>
       <c r="FN7" t="n">
-        <v>1.488589168729959e-05</v>
+        <v>2.183963323772534e-14</v>
       </c>
       <c r="FO7" t="n">
-        <v>3.629616549005732e-05</v>
+        <v>1.027856998733062e-13</v>
       </c>
       <c r="FP7" t="n">
-        <v>5.092551418783842e-06</v>
+        <v>3.629154675345234e-14</v>
       </c>
       <c r="FQ7" t="n">
-        <v>2.696477167773992e-05</v>
+        <v>1.493063349821896e-13</v>
       </c>
       <c r="FR7" t="n">
-        <v>1.195568984257989e-06</v>
+        <v>4.792322680184646e-14</v>
       </c>
       <c r="FS7" t="n">
-        <v>1.109576078306418e-05</v>
+        <v>6.552978239248233e-14</v>
       </c>
       <c r="FT7" t="n">
-        <v>2.957038668682799e-05</v>
+        <v>1.757046385556654e-13</v>
       </c>
       <c r="FU7" t="n">
-        <v>1.092001548386179e-05</v>
+        <v>7.805529226440067e-14</v>
       </c>
       <c r="FV7" t="n">
-        <v>2.210044840467162e-06</v>
+        <v>1.687767899613904e-13</v>
       </c>
       <c r="FW7" t="n">
-        <v>7.884979822847527e-06</v>
+        <v>1.163656031342303e-13</v>
       </c>
       <c r="FX7" t="n">
-        <v>1.313979464612203e-05</v>
+        <v>1.252499216538097e-13</v>
       </c>
       <c r="FY7" t="n">
-        <v>1.062155661202269e-05</v>
+        <v>5.855983287259697e-14</v>
       </c>
       <c r="FZ7" t="n">
-        <v>2.255229082948063e-05</v>
+        <v>9.124093895782753e-14</v>
       </c>
       <c r="GA7" t="n">
-        <v>6.412699349311879e-06</v>
+        <v>2.571576103644647e-14</v>
       </c>
       <c r="GB7" t="n">
-        <v>2.409351873211563e-05</v>
+        <v>9.783277974632215e-14</v>
       </c>
       <c r="GC7" t="n">
-        <v>2.626524474180769e-05</v>
+        <v>7.150893375704181e-14</v>
       </c>
       <c r="GD7" t="n">
-        <v>1.498328765592305e-05</v>
+        <v>1.76034317331264e-13</v>
       </c>
       <c r="GE7" t="n">
-        <v>1.56677970153396e-06</v>
+        <v>3.201351537378619e-14</v>
       </c>
       <c r="GF7" t="n">
-        <v>4.826398253499065e-06</v>
+        <v>8.781546995649536e-14</v>
       </c>
       <c r="GG7" t="n">
-        <v>4.017361334263114e-06</v>
+        <v>4.612426773528168e-14</v>
       </c>
     </row>
     <row r="8">
@@ -4982,3985 +4982,3985 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.001388030825182796</v>
+        <v>0.001475423341616988</v>
       </c>
       <c r="B9" t="n">
-        <v>0.07222412526607513</v>
+        <v>0.001213205978274345</v>
       </c>
       <c r="C9" t="n">
-        <v>0.005384511779993773</v>
+        <v>0.0006279737572185695</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05126983299851418</v>
+        <v>0.003641362069174647</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02111444063484669</v>
+        <v>0.00108509452547878</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01440095528960228</v>
+        <v>0.002987069310620427</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006264252588152885</v>
+        <v>0.003186930902302265</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01318130828440189</v>
+        <v>0.002195237437263131</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01725742220878601</v>
+        <v>0.0003807842149399221</v>
       </c>
       <c r="J9" t="n">
-        <v>0.008100705221295357</v>
+        <v>0.0009361705742776394</v>
       </c>
       <c r="K9" t="n">
-        <v>0.05484284460544586</v>
+        <v>0.0007255329983308911</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002716048387810588</v>
+        <v>0.0003831207286566496</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04516667872667313</v>
+        <v>0.005334303714334965</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02967613376677036</v>
+        <v>0.002395595191046596</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02266972325742245</v>
+        <v>0.003279968164861202</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002151068765670061</v>
+        <v>0.003426173469051719</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001833979855291545</v>
+        <v>0.0007138571236282587</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01884905062615871</v>
+        <v>0.0001503526291344315</v>
       </c>
       <c r="S9" t="n">
-        <v>0.003596615511924028</v>
+        <v>0.001068905927240849</v>
       </c>
       <c r="T9" t="n">
-        <v>0.007794694975018501</v>
+        <v>0.0001026993850246072</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002279275096952915</v>
+        <v>0.0008584323222748935</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01472442597150803</v>
+        <v>2.167478669434786e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01392319239675999</v>
+        <v>0.0004845478397328407</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001965084578841925</v>
+        <v>0.001268825610168278</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.005466834176331758</v>
+        <v>2.147228224202991e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.007337163668125868</v>
+        <v>0.0008633433026261628</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01031944248825312</v>
+        <v>0.0001756833080435172</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0002253437414765358</v>
+        <v>0.001309165847487748</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.01422496046870947</v>
+        <v>0.0005679414025507867</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.002021654276177287</v>
+        <v>0.001016968861222267</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.006825271993875504</v>
+        <v>0.0001764076005201787</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.002776754088699818</v>
+        <v>0.0009927640203386545</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.01544380839914083</v>
+        <v>0.001263981219381094</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.002686169929802418</v>
+        <v>0.0001218381221406162</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.0003040750743821263</v>
+        <v>0.0008749774424359202</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.003771473420783877</v>
+        <v>0.0009233156451955438</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.004834791645407677</v>
+        <v>0.001001492142677307</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.005897066555917263</v>
+        <v>0.001084203599020839</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0008479479001834989</v>
+        <v>0.0009111188701353967</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.002137589734047651</v>
+        <v>0.0009111938998103142</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.01281793043017387</v>
+        <v>0.0001401834888383746</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.01298465579748154</v>
+        <v>0.001005445024929941</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.00214836373925209</v>
+        <v>0.001214241143316031</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.004759861156344414</v>
+        <v>0.0006444586906582117</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.007547311950474977</v>
+        <v>0.0004538692883215845</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.005398389883339405</v>
+        <v>0.001489866641350091</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.05192543938755989</v>
+        <v>0.001149710733443499</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.002131260232999921</v>
+        <v>0.001054074848070741</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.01165355648845434</v>
+        <v>0.0009514932753518224</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.003877822309732437</v>
+        <v>0.002921805717051029</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.01135455537587404</v>
+        <v>0.002538955071941018</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.01197901554405689</v>
+        <v>0.0001349898520857096</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.01632342115044594</v>
+        <v>0.0002837492502294481</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.006756075657904148</v>
+        <v>0.0001252146903425455</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.003729577176272869</v>
+        <v>0.0009566079825162888</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.01120072789490223</v>
+        <v>8.089391485555097e-05</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.01273740082979202</v>
+        <v>0.0003015398979187012</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.01313216611742973</v>
+        <v>0.0005613324465230107</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.02023005299270153</v>
+        <v>0.001494679134339094</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.01301634684205055</v>
+        <v>0.0003220192447770387</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.008072863332927227</v>
+        <v>0.0008682964835315943</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0009059433359652758</v>
+        <v>0.001025046920403838</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.01435607485473156</v>
+        <v>0.0005264938808977604</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.009242375381290913</v>
+        <v>0.0001415236911270767</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.01850976049900055</v>
+        <v>0.001185364089906216</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.006779011804610491</v>
+        <v>2.05336109502241e-05</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.00245585385710001</v>
+        <v>0.001653724699281156</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.01873229630291462</v>
+        <v>0.0006069706287235022</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.004300143104046583</v>
+        <v>0.0007972619496285915</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.004597045481204987</v>
+        <v>3.504296182654798e-05</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.005544482730329037</v>
+        <v>0.0003325814031995833</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.00739467004314065</v>
+        <v>0.0005307876272127032</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.004260109271854162</v>
+        <v>0.000586597656365484</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.02535497769713402</v>
+        <v>0.001139011583290994</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.008970074355602264</v>
+        <v>0.0003127677773591131</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.01081035286188126</v>
+        <v>0.002593285869807005</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.00199058884754777</v>
+        <v>0.0005334421875886619</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.001931444043293595</v>
+        <v>0.001274547656066716</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.004107999615371227</v>
+        <v>0.0001651224592933431</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.01166608463972807</v>
+        <v>0.0002322669170098379</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.01310958340764046</v>
+        <v>0.0004641977720893919</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.001926285680383444</v>
+        <v>0.0002713185676839203</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.01288500148802996</v>
+        <v>0.0003858751733787358</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.004940483719110489</v>
+        <v>0.0002754249435383826</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.005972390063107014</v>
+        <v>0.001473134383559227</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.001242783269844949</v>
+        <v>0.0001949617872014642</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.002723330399021506</v>
+        <v>0.0005485477158799767</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.001721725682727993</v>
+        <v>0.0002388195716775954</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.003200195729732513</v>
+        <v>0.0004744925536215305</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.0006100772880017757</v>
+        <v>1.283622987102717e-05</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.0138420881703496</v>
+        <v>0.000214032712392509</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.005991667509078979</v>
+        <v>0.0006755227223038673</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.002458881121128798</v>
+        <v>0.0008559220004826784</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.01554596982896328</v>
+        <v>0.001470622257329524</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.007251041475683451</v>
+        <v>0.0001668199838604778</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.007910802029073238</v>
+        <v>0.0004574163176584989</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.01586773991584778</v>
+        <v>0.001105084083974361</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.01709382794797421</v>
+        <v>0.0004592761979438365</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.002631379524245858</v>
+        <v>0.0009074366535060108</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.002914738841354847</v>
+        <v>0.0003572394489310682</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.01043492835015059</v>
+        <v>0.0002155800466425717</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.006473959423601627</v>
+        <v>0.000159542600158602</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.007475744932889938</v>
+        <v>0.001626000390388072</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.001915551838465035</v>
+        <v>0.0006977330194786191</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.001690038363449275</v>
+        <v>0.0005633982946164906</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.003287546569481492</v>
+        <v>0.0002542355796322227</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.00517432764172554</v>
+        <v>0.0004238734254613519</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0006775385700166225</v>
+        <v>0.0002358785131946206</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.006442049518227577</v>
+        <v>0.0001915544271469116</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.005308083258569241</v>
+        <v>0.0003683008544612676</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.0002319292980246246</v>
+        <v>0.0001764358312357217</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.02660442143678665</v>
+        <v>0.0008254211861640215</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.02042249031364918</v>
+        <v>0.0007697420660406351</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.01025415025651455</v>
+        <v>0.00186932273209095</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.004752566572278738</v>
+        <v>0.0006634853198193014</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.01067000720649958</v>
+        <v>0.003023414872586727</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.00684682372957468</v>
+        <v>0.0009313313057646155</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.001862129778601229</v>
+        <v>0.0008230404928326607</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.004976361989974976</v>
+        <v>0.0006428815540857613</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.007287402637302876</v>
+        <v>0.000309108174405992</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.001980185974389315</v>
+        <v>9.233539458364248e-06</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.005924955941736698</v>
+        <v>0.0009064477635547519</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.004618095234036446</v>
+        <v>0.0006284458213485777</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.007491558790206909</v>
+        <v>6.068468792364001e-06</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.0001936207991093397</v>
+        <v>0.001521617872640491</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.00705672474578023</v>
+        <v>0.002310999669134617</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.00112191669177264</v>
+        <v>0.0003816703683696687</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.001300028408877552</v>
+        <v>0.0002006758295465261</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.006999420467764139</v>
+        <v>0.0009620480705052614</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.002971164882183075</v>
+        <v>0.0005057358066551387</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.001498915371485054</v>
+        <v>0.0005506754387170076</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.004018097650259733</v>
+        <v>0.001271392917260528</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.002547867363318801</v>
+        <v>0.0006942811887711287</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.005285682622343302</v>
+        <v>0.001631845370866358</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.002376536140218377</v>
+        <v>0.001326239202171564</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.002059947932139039</v>
+        <v>0.0004185287980362773</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.009036663919687271</v>
+        <v>0.0002194971602875739</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.003960156813263893</v>
+        <v>0.0008671590476296842</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.004657259676605463</v>
+        <v>0.001485555665567517</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.009243406355381012</v>
+        <v>0.0002750144631136209</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0005059755058027804</v>
+        <v>0.0004651923081837595</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.002864050213247538</v>
+        <v>0.0001569370797369629</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.00188380409963429</v>
+        <v>0.0001307908969465643</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.001512638758867979</v>
+        <v>0.000144615798490122</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.0026941136457026</v>
+        <v>0.0002537851396482438</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.01060123555362225</v>
+        <v>0.0007501975633203983</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.005213665775954723</v>
+        <v>7.858140452299267e-05</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.002732703927904367</v>
+        <v>0.002087107859551907</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.000247028743615374</v>
+        <v>6.177753675729036e-05</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.006989222019910812</v>
+        <v>0.0005291698034852743</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.01204715482890606</v>
+        <v>0.0004106832202523947</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.01304518058896065</v>
+        <v>0.0006627841503359377</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0006248960271477699</v>
+        <v>0.001753944205120206</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0003436742990743369</v>
+        <v>0.0002591541851870716</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.01007035188376904</v>
+        <v>0.0004645476583391428</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.00362318754196167</v>
+        <v>0.0002840791712515056</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.00715695321559906</v>
+        <v>0.001629461301490664</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.00402125297114253</v>
+        <v>0.0002602957538329065</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0007031434215605259</v>
+        <v>0.0006161805358715355</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.00376830855384469</v>
+        <v>0.0004415694274939597</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.005291434470564127</v>
+        <v>0.0005759206251241267</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.003681384492665529</v>
+        <v>7.220009138109162e-05</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.00143709871917963</v>
+        <v>0.0003829748020507395</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0007265193853527308</v>
+        <v>9.936637070495635e-05</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.006009954027831554</v>
+        <v>0.0003753594937734306</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.004641881678253412</v>
+        <v>0.0005226354114711285</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.007090796250849962</v>
+        <v>0.0005810800357721746</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.0001515849580755457</v>
+        <v>2.609976218082011e-05</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.001379805384203792</v>
+        <v>0.0005279890028759837</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.0006114827701821923</v>
+        <v>0.0009514171979390085</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.00532367592677474</v>
+        <v>3.319437382742763e-05</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.008673477917909622</v>
+        <v>0.001335083157755435</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.003672293620184064</v>
+        <v>0.0008988454937934875</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.009249378927052021</v>
+        <v>0.00163436948787421</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.006999802775681019</v>
+        <v>0.0007183399284258485</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.01972070522606373</v>
+        <v>0.001971227116882801</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.003896364476531744</v>
+        <v>0.001058017136529088</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.009251036681234837</v>
+        <v>0.0006518379668705165</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.005011385306715965</v>
+        <v>0.00377475842833519</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.005817837081849575</v>
+        <v>0.0009886490879580379</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.01374700572341681</v>
+        <v>0.0004289579228498042</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.000782548391725868</v>
+        <v>0.0007645508740097284</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.006620829459279776</v>
+        <v>0.0003822965081781149</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.004237602464854717</v>
+        <v>0.001341141178272665</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.001580902026034892</v>
+        <v>7.170405297074467e-05</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.01424464583396912</v>
+        <v>0.00175060797482729</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.02463102526962757</v>
+        <v>0.0006868673372082412</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.003267141524702311</v>
+        <v>0.001024910248816013</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.0008420302765443921</v>
+        <v>2.656698052305728e-05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.2233625054359436</v>
+        <v>0.04290911182761192</v>
       </c>
       <c r="B10" t="n">
-        <v>1.608471870422363</v>
+        <v>0.02822648361325264</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1916362345218658</v>
+        <v>0.02067187242209911</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3821955919265747</v>
+        <v>0.2581838071346283</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04735937714576721</v>
+        <v>0.07685226947069168</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2457804977893829</v>
+        <v>0.03910859301686287</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1552047878503799</v>
+        <v>0.1400125622749329</v>
       </c>
       <c r="H10" t="n">
-        <v>0.08166024088859558</v>
+        <v>0.1318784952163696</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06349936127662659</v>
+        <v>0.08721479773521423</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2793794870376587</v>
+        <v>0.03902082145214081</v>
       </c>
       <c r="K10" t="n">
-        <v>1.215038061141968</v>
+        <v>0.04905446618795395</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0413997694849968</v>
+        <v>0.02226174809038639</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3984889388084412</v>
+        <v>0.3534384667873383</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1034842729568481</v>
+        <v>0.1246628165245056</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2398803979158401</v>
+        <v>0.0417306050658226</v>
       </c>
       <c r="P10" t="n">
-        <v>0.105275571346283</v>
+        <v>0.1877960562705994</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1128651350736618</v>
+        <v>0.1109936162829399</v>
       </c>
       <c r="R10" t="n">
-        <v>0.002079151570796967</v>
+        <v>0.1006755828857422</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01887862756848335</v>
+        <v>0.02519336715340614</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1856917291879654</v>
+        <v>0.01305330451577902</v>
       </c>
       <c r="U10" t="n">
-        <v>0.04825019836425781</v>
+        <v>0.01317891757935286</v>
       </c>
       <c r="V10" t="n">
-        <v>0.145618811249733</v>
+        <v>0.03420587256550789</v>
       </c>
       <c r="W10" t="n">
-        <v>0.125423401594162</v>
+        <v>0.07672352343797684</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1581019461154938</v>
+        <v>0.007857417687773705</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.07094833254814148</v>
+        <v>0.009361888282001019</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.1625893712043762</v>
+        <v>0.007704640738666058</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.1421013325452805</v>
+        <v>0.009169317781925201</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.003172382712364197</v>
+        <v>0.009689159691333771</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1515527218580246</v>
+        <v>0.005172901786863804</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.1627711206674576</v>
+        <v>0.006767264101654291</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.04054556414484978</v>
+        <v>0.01478573866188526</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1628932654857635</v>
+        <v>0.01034271530807018</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.1010901555418968</v>
+        <v>0.01748403534293175</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.1204488575458527</v>
+        <v>0.03737467527389526</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.05846241116523743</v>
+        <v>0.03503824025392532</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.1013962030410767</v>
+        <v>0.01644532755017281</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.1534448266029358</v>
+        <v>0.03343882784247398</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.1327441036701202</v>
+        <v>0.04051148518919945</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.00184256536886096</v>
+        <v>0.02914762124419212</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.0923854261636734</v>
+        <v>0.05154972895979881</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.08784933388233185</v>
+        <v>0.03588880598545074</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.1688950508832932</v>
+        <v>0.02396618388593197</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.03698927164077759</v>
+        <v>0.07371681928634644</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.08754171431064606</v>
+        <v>0.003046491649001837</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.07362419366836548</v>
+        <v>0.01999625004827976</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.02087578549981117</v>
+        <v>0.1129310578107834</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.9302986264228821</v>
+        <v>0.02633781172335148</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.08747054636478424</v>
+        <v>0.05721251666545868</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.04828928411006927</v>
+        <v>0.06801363825798035</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.07891088724136353</v>
+        <v>0.1474387794733047</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.1149126216769218</v>
+        <v>0.02578624896705151</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.02543869987130165</v>
+        <v>0.02082864008843899</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.1412197053432465</v>
+        <v>0.004415103700011969</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.1120565235614777</v>
+        <v>0.03992350026965141</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.07413193583488464</v>
+        <v>0.02059090510010719</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.3916251957416534</v>
+        <v>0.001540433615446091</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.1621261090040207</v>
+        <v>0.02569029480218887</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.05961291491985321</v>
+        <v>0.04179401323199272</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.3038046956062317</v>
+        <v>0.04289169982075691</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.02837271615862846</v>
+        <v>0.01086060144007206</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.110341876745224</v>
+        <v>0.01917042769491673</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.1950941532850266</v>
+        <v>0.06128203868865967</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.04378002509474754</v>
+        <v>0.01237275544553995</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.1787276566028595</v>
+        <v>0.01184968836605549</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.2327460497617722</v>
+        <v>0.07048667967319489</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.1140723377466202</v>
+        <v>0.05410970374941826</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.09183854609727859</v>
+        <v>0.06858546286821365</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.09068095684051514</v>
+        <v>0.02743045799434185</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.01330671738833189</v>
+        <v>0.0006791608175262809</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.02150797471404076</v>
+        <v>0.001655407249927521</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.1080965846776962</v>
+        <v>0.004755796864628792</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.05826115608215332</v>
+        <v>0.007173065096139908</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.07643125206232071</v>
+        <v>0.03664760664105415</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.5110538005828857</v>
+        <v>0.02782686613500118</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.08427345007658005</v>
+        <v>0.02813013456761837</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.01350155100226402</v>
+        <v>0.1373195946216583</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.04611208289861679</v>
+        <v>0.07549912482500076</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.1653588712215424</v>
+        <v>0.02000217884778976</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.09439253062009811</v>
+        <v>0.01704857498407364</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.005655620247125626</v>
+        <v>0.008335059508681297</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.1685236394405365</v>
+        <v>0.01971384137868881</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.07918134331703186</v>
+        <v>0.01470424979925156</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.2675209641456604</v>
+        <v>0.009820332750678062</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.04046197235584259</v>
+        <v>0.02294847927987576</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.02437657862901688</v>
+        <v>0.08625590801239014</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.1103634536266327</v>
+        <v>0.01992331445217133</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.01294903829693794</v>
+        <v>0.001562674064189196</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.0415879413485527</v>
+        <v>0.005258641671389341</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.003939906135201454</v>
+        <v>0.02622526697814465</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0539083369076252</v>
+        <v>0.008495232090353966</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.1664513945579529</v>
+        <v>0.02988449484109879</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.112221896648407</v>
+        <v>0.01314971409738064</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.04653208702802658</v>
+        <v>0.02055495977401733</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.2547058761119843</v>
+        <v>0.1041709333658218</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.2078319787979126</v>
+        <v>0.03514335677027702</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.2431214153766632</v>
+        <v>0.01784563064575195</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.1361177265644073</v>
+        <v>0.07168540358543396</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.1086809709668159</v>
+        <v>0.02025369741022587</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.02163647674024105</v>
+        <v>0.03540144860744476</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.07524199783802032</v>
+        <v>0.009965009987354279</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.2451775670051575</v>
+        <v>0.01581205986440182</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.05745023861527443</v>
+        <v>0.01963128335773945</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0790950283408165</v>
+        <v>0.09564414620399475</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.1328696310520172</v>
+        <v>0.03148606047034264</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.05153369531035423</v>
+        <v>0.002416049130260944</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.04905080050230026</v>
+        <v>0.005413867998868227</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.01378617808222771</v>
+        <v>0.02865510061383247</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.01887235976755619</v>
+        <v>0.02023540437221527</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.03162387013435364</v>
+        <v>0.07267819344997406</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.3605613708496094</v>
+        <v>0.01491952873766422</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.07049767673015594</v>
+        <v>0.03840730339288712</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.2381770312786102</v>
+        <v>0.1083791851997375</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.002546886913478374</v>
+        <v>0.03530998155474663</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.09556308388710022</v>
+        <v>0.0843810960650444</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.1355932056903839</v>
+        <v>0.002517483429983258</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.04753979295492172</v>
+        <v>0.0895017683506012</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.03940964862704277</v>
+        <v>0.03175504505634308</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.116410069167614</v>
+        <v>0.04761568456888199</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.1535128355026245</v>
+        <v>0.01756862923502922</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.05806272849440575</v>
+        <v>0.01514785550534725</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.04693510755896568</v>
+        <v>0.02200022526085377</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.1308248341083527</v>
+        <v>0.01483178697526455</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.1463225185871124</v>
+        <v>0.02833903208374977</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.01026292610913515</v>
+        <v>0.02475864440202713</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.1175606772303581</v>
+        <v>0.05635987222194672</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.01324767898768187</v>
+        <v>0.07935480773448944</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.04082127287983894</v>
+        <v>0.02443317323923111</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.02094811014831066</v>
+        <v>0.03404858708381653</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.1402338445186615</v>
+        <v>0.05357251688838005</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.004431562963873148</v>
+        <v>0.04262805357575417</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.2019893974065781</v>
+        <v>0.02871473133563995</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.01216772757470608</v>
+        <v>0.02349644340574741</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.00368160055950284</v>
+        <v>0.01289534289389849</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.01889888010919094</v>
+        <v>0.07406561821699142</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.05479365959763527</v>
+        <v>0.01452109776437283</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.04272947087883949</v>
+        <v>0.05569789931178093</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.2152293920516968</v>
+        <v>0.01623716950416565</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.01652428694069386</v>
+        <v>0.003079547081142664</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0138050178065896</v>
+        <v>0.09069147706031799</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.01810695603489876</v>
+        <v>0.008582023903727531</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.01087374426424503</v>
+        <v>0.009154491126537323</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.05528437718749046</v>
+        <v>0.01408172398805618</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.03604356944561005</v>
+        <v>0.01884871162474155</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.07246138155460358</v>
+        <v>0.01890793442726135</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.03936076536774635</v>
+        <v>0.02605351433157921</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.1382226347923279</v>
+        <v>0.02363113686442375</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.02206674218177795</v>
+        <v>0.01204256247729063</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.04725569859147072</v>
+        <v>0.08717750012874603</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.15639728307724</v>
+        <v>0.02206127345561981</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.2485509216785431</v>
+        <v>0.009417809545993805</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.1227478682994843</v>
+        <v>0.02150065079331398</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.09999896585941315</v>
+        <v>0.03754756972193718</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.03207907825708389</v>
+        <v>0.07870122045278549</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.05530006438493729</v>
+        <v>0.01709398813545704</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.2615103125572205</v>
+        <v>0.003149643773213029</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.01970895938575268</v>
+        <v>0.01193672139197588</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.04889020696282387</v>
+        <v>0.09877966344356537</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.09128886461257935</v>
+        <v>0.02450105920433998</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.04620701819658279</v>
+        <v>0.009711753576993942</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.06723719090223312</v>
+        <v>0.003053072839975357</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.005013780668377876</v>
+        <v>0.03284896165132523</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.05543257296085358</v>
+        <v>0.009511790238320827</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.04552160203456879</v>
+        <v>0.00770452618598938</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.07817556709051132</v>
+        <v>0.02287538908421993</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.01120554096996784</v>
+        <v>0.001492116134613752</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.1200622692704201</v>
+        <v>0.02558732964098454</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.1307873278856277</v>
+        <v>0.006094498094171286</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.03579414635896683</v>
+        <v>0.02917313203215599</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.01489011477679014</v>
+        <v>0.02567063644528389</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.001489525660872459</v>
+        <v>0.01176045648753643</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.1183484718203545</v>
+        <v>0.0173074696213007</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.04971495270729065</v>
+        <v>0.03308694809675217</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.01659679040312767</v>
+        <v>0.03707538545131683</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.09412901848554611</v>
+        <v>0.03369439020752907</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.1579976677894592</v>
+        <v>0.01911072246730328</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.07792634516954422</v>
+        <v>0.002717834897339344</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.1083278208971024</v>
+        <v>0.01657334715127945</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.08166053146123886</v>
+        <v>0.05999650061130524</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.1166855543851852</v>
+        <v>0.1031046584248543</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.02450686134397984</v>
+        <v>0.02133771404623985</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.1413055956363678</v>
+        <v>0.002270427066832781</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.04205072671175003</v>
+        <v>0.01050928607583046</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.02043166570365429</v>
+        <v>0.04244204983115196</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.02139310538768768</v>
+        <v>0.05270770192146301</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.2849186360836029</v>
+        <v>0.02242190577089787</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.2133898437023163</v>
+        <v>0.05848011001944542</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.3507100045681</v>
+        <v>0.02486437745392323</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.1002355888485909</v>
+        <v>0.03045722097158432</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.01294368226081133</v>
+        <v>0.03133897483348846</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.003612309694290161</v>
+        <v>0.01169934030622244</v>
       </c>
       <c r="B11" t="n">
-        <v>0.03215642645955086</v>
+        <v>0.3665460348129272</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001000768737867475</v>
+        <v>0.08219638466835022</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01115056313574314</v>
+        <v>0.3081526458263397</v>
       </c>
       <c r="E11" t="n">
-        <v>0.005994324572384357</v>
+        <v>0.437460720539093</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01928339339792728</v>
+        <v>0.4679822325706482</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002596558071672916</v>
+        <v>0.1806561350822449</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01754504814743996</v>
+        <v>0.3651193380355835</v>
       </c>
       <c r="I11" t="n">
-        <v>0.003226690227165818</v>
+        <v>0.001438111066818237</v>
       </c>
       <c r="J11" t="n">
-        <v>0.002462648088112473</v>
+        <v>0.006457008421421051</v>
       </c>
       <c r="K11" t="n">
-        <v>0.03373114764690399</v>
+        <v>0.5077831745147705</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001886029960587621</v>
+        <v>0.1387253403663635</v>
       </c>
       <c r="M11" t="n">
-        <v>0.002249879762530327</v>
+        <v>0.1112766414880753</v>
       </c>
       <c r="N11" t="n">
-        <v>0.003850746201351285</v>
+        <v>0.8331764340400696</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01408699527382851</v>
+        <v>0.5501484274864197</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0007421276532113552</v>
+        <v>0.1205044984817505</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01529556233435869</v>
+        <v>0.1002525165677071</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0109275821596384</v>
+        <v>0.2212903946638107</v>
       </c>
       <c r="S11" t="n">
-        <v>7.597566582262516e-05</v>
+        <v>0.09077171981334686</v>
       </c>
       <c r="T11" t="n">
-        <v>0.003469044808298349</v>
+        <v>0.07471270859241486</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001638606307096779</v>
+        <v>0.201549232006073</v>
       </c>
       <c r="V11" t="n">
-        <v>0.005428227595984936</v>
+        <v>0.2397260218858719</v>
       </c>
       <c r="W11" t="n">
-        <v>0.02304547466337681</v>
+        <v>0.2410848438739777</v>
       </c>
       <c r="X11" t="n">
-        <v>0.008436418138444424</v>
+        <v>0.1937520503997803</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.00162814452778548</v>
+        <v>0.01839360594749451</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0109576191753149</v>
+        <v>0.0008349716663360596</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.005423240829259157</v>
+        <v>0.0865488275885582</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0001618142705410719</v>
+        <v>0.2326480597257614</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.001850485103204846</v>
+        <v>0.1237220615148544</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.003856166498735547</v>
+        <v>0.02456609904766083</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.001815415802411735</v>
+        <v>0.2848127782344818</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.002534373430535197</v>
+        <v>0.1316877901554108</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.005840914789587259</v>
+        <v>0.09851966053247452</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.002190015744417906</v>
+        <v>0.1190571188926697</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0001042378135025501</v>
+        <v>0.1286632120609283</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.00196999660693109</v>
+        <v>0.06612490117549896</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.001750662224367261</v>
+        <v>0.08684206008911133</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.002954668132588267</v>
+        <v>0.1362740099430084</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.001408456126227975</v>
+        <v>0.08812001347541809</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.005149911157786846</v>
+        <v>0.1533119082450867</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.006191323045641184</v>
+        <v>0.2405353784561157</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.005456538870930672</v>
+        <v>0.04105215519666672</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.0009241667576134205</v>
+        <v>0.1797295212745667</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.000626235269010067</v>
+        <v>0.01222194358706474</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.002323266584426165</v>
+        <v>0.02534700557589531</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.003325474914163351</v>
+        <v>0.09630429744720459</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.01194607373327017</v>
+        <v>0.9642786979675293</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.002677640179172158</v>
+        <v>0.1049600690603256</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.01019448693841696</v>
+        <v>0.05309481918811798</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.01017841417342424</v>
+        <v>0.1073320657014847</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.01883669570088387</v>
+        <v>0.143486276268959</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.0118706738576293</v>
+        <v>0.3302693367004395</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.005442416295409203</v>
+        <v>0.05329447612166405</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.003712966106832027</v>
+        <v>0.1016530394554138</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.003784481436014175</v>
+        <v>0.1707443445920944</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.01545028202235699</v>
+        <v>0.2770855128765106</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.005925743840634823</v>
+        <v>0.01154755800962448</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.00208181468769908</v>
+        <v>0.4779419302940369</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.002086641732603312</v>
+        <v>0.09406653046607971</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.004153074230998755</v>
+        <v>0.08769971132278442</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.008842229843139648</v>
+        <v>0.1789247691631317</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.007005203049629927</v>
+        <v>0.2365497350692749</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.008377964608371258</v>
+        <v>0.02292549610137939</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.004563343711197376</v>
+        <v>0.009486645460128784</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.005033494904637337</v>
+        <v>0.3777961432933807</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.0004698566044680774</v>
+        <v>0.1047661453485489</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.01066391728818417</v>
+        <v>0.01701142638921738</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0039213583804667</v>
+        <v>0.3528286814689636</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.001053671236149967</v>
+        <v>0.3105882704257965</v>
       </c>
       <c r="BR11" t="n">
-        <v>8.144578896462917e-05</v>
+        <v>0.09611165523529053</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.007209776435047388</v>
+        <v>0.03761971369385719</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.002162886317819357</v>
+        <v>0.09248048067092896</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.001117916312068701</v>
+        <v>0.01440998911857605</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.008959745988249779</v>
+        <v>0.5327009558677673</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.0005795119795948267</v>
+        <v>0.07049243897199631</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.004020345397293568</v>
+        <v>0.5751960277557373</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.000291756761725992</v>
+        <v>0.1497549414634705</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.006893620826303959</v>
+        <v>0.1695814430713654</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.005991595331579447</v>
+        <v>0.05817071348428726</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.005353639367967844</v>
+        <v>0.1030301824212074</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.001957465661689639</v>
+        <v>0.1977231353521347</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.412095586303622e-05</v>
+        <v>0.1981570869684219</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.003375827334821224</v>
+        <v>0.1278493702411652</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.001974539365619421</v>
+        <v>0.05489668622612953</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.000895505421794951</v>
+        <v>0.03237710148096085</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.001607937505468726</v>
+        <v>0.1177630126476288</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.002727025654166937</v>
+        <v>0.1429267674684525</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.002654412295669317</v>
+        <v>0.07969218492507935</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.004750774241983891</v>
+        <v>0.01690309680998325</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.00239961058832705</v>
+        <v>0.01334782689809799</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.001125923707149923</v>
+        <v>0.1526966392993927</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.0005301045021042228</v>
+        <v>0.4320870935916901</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.0002450190950185061</v>
+        <v>0.01385125517845154</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.008196072652935982</v>
+        <v>0.1034739166498184</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.0006224026437848806</v>
+        <v>0.1759382635354996</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.001363616436719894</v>
+        <v>0.05763880908489227</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.009520268999040127</v>
+        <v>0.0998254269361496</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.002428460167720914</v>
+        <v>0.07771404087543488</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.006878321059048176</v>
+        <v>0.1450114250183105</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.0004871436394751072</v>
+        <v>0.1518777459859848</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.003313706489279866</v>
+        <v>0.07770363986492157</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.001300782896578312</v>
+        <v>0.01115890964865685</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.0001462994841858745</v>
+        <v>0.01740017905831337</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0006148382090032101</v>
+        <v>0.1142765134572983</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.000307023903587833</v>
+        <v>0.1283639520406723</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.001843409263528883</v>
+        <v>0.06237522885203362</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.004606011789292097</v>
+        <v>0.004928148351609707</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.001970495795831084</v>
+        <v>0.004852473270148039</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.01072893384844065</v>
+        <v>0.1619480103254318</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.01110876724123955</v>
+        <v>0.2239625006914139</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.0001996285282075405</v>
+        <v>0.01109499018639326</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.0201503150165081</v>
+        <v>0.09002930670976639</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.007071170024573803</v>
+        <v>0.08524309098720551</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.01628063805401325</v>
+        <v>0.103281557559967</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.0007018130272626877</v>
+        <v>0.01722733676433563</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.004656302742660046</v>
+        <v>0.4339597821235657</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.007017859257757664</v>
+        <v>0.2020544707775116</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.002274686703458428</v>
+        <v>0.07759854197502136</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.001902920892462134</v>
+        <v>0.0932336151599884</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.004698950797319412</v>
+        <v>0.00176285021007061</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.004243539180606604</v>
+        <v>0.1408116817474365</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.007891814224421978</v>
+        <v>0.06932458281517029</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.001333722379058599</v>
+        <v>0.08900326490402222</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.004298956133425236</v>
+        <v>0.2146587818861008</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.000174160348251462</v>
+        <v>0.1449036002159119</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.003762611420825124</v>
+        <v>0.02900495752692223</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0001671599457040429</v>
+        <v>0.06067909300327301</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0004119708610232919</v>
+        <v>0.1118369996547699</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.003608294297009706</v>
+        <v>0.06262777000665665</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.005731252022087574</v>
+        <v>0.08018191158771515</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.00746849225834012</v>
+        <v>0.23377725481987</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.004860176704823971</v>
+        <v>0.07085332274436951</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.002681996207684278</v>
+        <v>0.05737995728850365</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.003104406874626875</v>
+        <v>0.02593152225017548</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.006417224649339914</v>
+        <v>0.1415469348430634</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.002186978003010154</v>
+        <v>0.1781964302062988</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.007772130891680717</v>
+        <v>0.05964143201708794</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.0009179529151879251</v>
+        <v>0.07153816521167755</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.006279219873249531</v>
+        <v>0.1029568836092949</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.001604735385626554</v>
+        <v>0.03829187154769897</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.003888355568051338</v>
+        <v>0.1887015253305435</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.0009061651071533561</v>
+        <v>0.03752942383289337</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.003229091409593821</v>
+        <v>0.04596276581287384</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.003620501607656479</v>
+        <v>0.02486075274646282</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.0008426273125223815</v>
+        <v>0.168568342924118</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.002706787781789899</v>
+        <v>0.1199310272932053</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.0003866222687065601</v>
+        <v>0.1094953864812851</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.003030731342732906</v>
+        <v>0.01291237026453018</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.002137607662007213</v>
+        <v>0.01028683874756098</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.003828433807939291</v>
+        <v>0.1315001845359802</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.00670969020575285</v>
+        <v>0.05917974188923836</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.01384283602237701</v>
+        <v>0.046702791005373</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.0003883135505020618</v>
+        <v>0.07107377797365189</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.000233922153711319</v>
+        <v>0.1975044310092926</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.003462275257334113</v>
+        <v>0.1305612772703171</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.001092244172468781</v>
+        <v>0.02140188217163086</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.001615732442587614</v>
+        <v>0.02508724480867386</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.001560353208333254</v>
+        <v>0.06141495332121849</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.001915118657052517</v>
+        <v>0.1342359185218811</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.004317504819482565</v>
+        <v>0.09902291744947433</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.006089545786380768</v>
+        <v>0.0237310416996479</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.003545294981449842</v>
+        <v>0.06540869921445847</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.005058979149907827</v>
+        <v>0.05593214556574821</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.0002328733098693192</v>
+        <v>0.1317511051893234</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.001691887155175209</v>
+        <v>0.04539778456091881</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.008696614764630795</v>
+        <v>0.207845151424408</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.0005187491187825799</v>
+        <v>0.0378570444881916</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.00154957571066916</v>
+        <v>0.01737226359546185</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.005453571677207947</v>
+        <v>0.09700044244527817</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.001667248550802469</v>
+        <v>0.2568601369857788</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.00204631919041276</v>
+        <v>0.00356373330578208</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.003810003399848938</v>
+        <v>0.04020997509360313</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.001002522767521441</v>
+        <v>0.05470147356390953</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.006286278367042542</v>
+        <v>0.165065199136734</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.0110482145100832</v>
+        <v>0.004274144768714905</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.02401169203221798</v>
+        <v>0.2238364815711975</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.007962442003190517</v>
+        <v>0.1042348444461823</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.008523828350007534</v>
+        <v>0.02908260002732277</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.003804652485996485</v>
+        <v>0.23787921667099</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.0001013199798762798</v>
+        <v>0.2213660478591919</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.006026638671755791</v>
+        <v>0.2280465215444565</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.004507407080382109</v>
+        <v>0.006490819156169891</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.0005885421996936202</v>
+        <v>0.1865597665309906</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.008129718713462353</v>
+        <v>0.02164219319820404</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.002303181448951364</v>
+        <v>0.02683328092098236</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.006327674724161625</v>
+        <v>0.1161532700061798</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.006131755188107491</v>
+        <v>0.03973338007926941</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.009684404358267784</v>
+        <v>0.0616827979683876</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.004790833219885826</v>
+        <v>0.2240303456783295</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.005162819288671017</v>
+        <v>0.0003842894511763006</v>
       </c>
       <c r="B12" t="n">
-        <v>0.07774706184864044</v>
+        <v>0.001315676025114954</v>
       </c>
       <c r="C12" t="n">
-        <v>0.001086618285626173</v>
+        <v>5.666768993251026e-05</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05441339686512947</v>
+        <v>0.00362884602509439</v>
       </c>
       <c r="E12" t="n">
-        <v>0.00358432624489069</v>
+        <v>0.0008331387070938945</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01164890266954899</v>
+        <v>0.001117041450925171</v>
       </c>
       <c r="G12" t="n">
-        <v>0.009829085320234299</v>
+        <v>0.002071161521598697</v>
       </c>
       <c r="H12" t="n">
-        <v>0.02063377387821674</v>
+        <v>0.001590825151652098</v>
       </c>
       <c r="I12" t="n">
-        <v>0.001874582725577056</v>
+        <v>0.0007003825157880783</v>
       </c>
       <c r="J12" t="n">
-        <v>0.001681547611951828</v>
+        <v>0.0004194165812805295</v>
       </c>
       <c r="K12" t="n">
-        <v>0.06279429048299789</v>
+        <v>0.0005025042919442058</v>
       </c>
       <c r="L12" t="n">
-        <v>0.008888130076229572</v>
+        <v>3.02798580378294e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>0.04370496422052383</v>
+        <v>0.004864082671701908</v>
       </c>
       <c r="N12" t="n">
-        <v>0.01279903762042522</v>
+        <v>0.001792519935406744</v>
       </c>
       <c r="O12" t="n">
-        <v>0.006564459763467312</v>
+        <v>0.00108928803820163</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0009109348757192492</v>
+        <v>0.002234560903161764</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.004775661509484053</v>
+        <v>0.0005511154886335135</v>
       </c>
       <c r="R12" t="n">
-        <v>0.005932248197495937</v>
+        <v>1.86315446626395e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>0.003722798777744174</v>
+        <v>0.0001320207084063441</v>
       </c>
       <c r="T12" t="n">
-        <v>0.01078091189265251</v>
+        <v>5.555880852625705e-05</v>
       </c>
       <c r="U12" t="n">
-        <v>0.003186217276379466</v>
+        <v>0.0004439103649929166</v>
       </c>
       <c r="V12" t="n">
-        <v>0.006812337785959244</v>
+        <v>0.0004915321478620172</v>
       </c>
       <c r="W12" t="n">
-        <v>0.009755060076713562</v>
+        <v>0.000740344577934593</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0005390716250985861</v>
+        <v>0.0006557762390002608</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.006136905867606401</v>
+        <v>6.36417098576203e-06</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.01040563359856606</v>
+        <v>0.0001225797459483147</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.01189470384269953</v>
+        <v>0.0001939865469466895</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.003321452066302299</v>
+        <v>8.367636473849416e-05</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.01583853922784328</v>
+        <v>0.0003505353815853596</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.003198884194716811</v>
+        <v>0.0002431334578432143</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0075719328597188</v>
+        <v>0.0002014592464547604</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.008099552243947983</v>
+        <v>0.0001490738359279931</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.006170153617858887</v>
+        <v>0.0006970639224164188</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.006703694351017475</v>
+        <v>0.0005033854977227747</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.003128308802843094</v>
+        <v>0.0002960628480650485</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.00505468063056469</v>
+        <v>0.0006763273850083351</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.005936024710536003</v>
+        <v>0.0002721947967074811</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.007840879261493683</v>
+        <v>0.000696561299264431</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.002443694276735187</v>
+        <v>0.0004943110980093479</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.004912788048386574</v>
+        <v>0.0008611062075942755</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.009838789701461792</v>
+        <v>0.0004126625135540962</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.01007937733083963</v>
+        <v>0.0006024519097991288</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.005879313684999943</v>
+        <v>0.001096127321943641</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.004842146765440702</v>
+        <v>0.000154433524585329</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.0006920717423781753</v>
+        <v>3.903789911419153e-05</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.004855172242969275</v>
+        <v>0.0008590805809944868</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.0563230849802494</v>
+        <v>0.0008989893831312656</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.004433922469615936</v>
+        <v>0.0008300486952066422</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.009941339492797852</v>
+        <v>0.0009927565697580576</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.01050978899002075</v>
+        <v>0.002227968536317348</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.002260185545310378</v>
+        <v>0.0007887525716796517</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.001340650720521808</v>
+        <v>4.034113953821361e-05</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.001896116300486028</v>
+        <v>0.0001138882798841223</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.0002041421248577535</v>
+        <v>0.0005096046370454133</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.01683665066957474</v>
+        <v>0.0002497094683349133</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.01311837509274483</v>
+        <v>0.0003121639601886272</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.01386342756450176</v>
+        <v>8.708165842108428e-05</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.006163192912936211</v>
+        <v>0.0002551051438786089</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.01704689301550388</v>
+        <v>0.0009872873779386282</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.008795308880507946</v>
+        <v>0.0005235098069533706</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.008226598612964153</v>
+        <v>0.0006836170796304941</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.008076619356870651</v>
+        <v>0.0007589670130982995</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.0009626965038478374</v>
+        <v>0.0005437584477476776</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.01094417832791805</v>
+        <v>0.0002474751090630889</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.01128753274679184</v>
+        <v>0.0006696312921121716</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.00682999799028039</v>
+        <v>0.0001365898351650685</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.003769969567656517</v>
+        <v>0.00118208525236696</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.01391876768320799</v>
+        <v>0.00067068514181301</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.007228078320622444</v>
+        <v>0.0001512506423750892</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.00249431561678648</v>
+        <v>0.0001821252080844715</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.006548880599439144</v>
+        <v>0.000108811364043504</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.00581548735499382</v>
+        <v>5.077852256363258e-05</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.005898383446037769</v>
+        <v>0.0002163631143048406</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.03094033896923065</v>
+        <v>0.0008051337208598852</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.000853453588206321</v>
+        <v>0.0004095632466487586</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.006518667098134756</v>
+        <v>0.002114716218784451</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.007663335651159286</v>
+        <v>0.0007164626149460673</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.006676372140645981</v>
+        <v>0.0008562524453736842</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.002017079154029489</v>
+        <v>0.0002159742289222777</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.005615847185254097</v>
+        <v>8.853319741319865e-06</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.01166645251214504</v>
+        <v>0.0002098602999467403</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.003253459930419922</v>
+        <v>4.08940322813578e-05</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.01416050083935261</v>
+        <v>0.0002666500222403556</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.003411876270547509</v>
+        <v>3.078032023040578e-05</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.005278118420392275</v>
+        <v>0.001305170357227325</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.004368361551314592</v>
+        <v>0.0001827140804380178</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.002863259520381689</v>
+        <v>0.0001749250513967127</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.005325521808117628</v>
+        <v>0.0001183571221190505</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.003267012070864439</v>
+        <v>0.0004949199501425028</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.002840069122612476</v>
+        <v>6.680600927211344e-05</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.02007104083895683</v>
+        <v>0.0004192824417259544</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.009973281063139439</v>
+        <v>0.0006460712756961584</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.004732572473585606</v>
+        <v>0.0006327236187644303</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.02007674239575863</v>
+        <v>0.001427810871973634</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.01562962122261524</v>
+        <v>0.0004364203196018934</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.01665357127785683</v>
+        <v>0.0003964335774071515</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.01646506413817406</v>
+        <v>0.0008842037059366703</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.02013462223112583</v>
+        <v>0.0003205417597200722</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.0004147113359067589</v>
+        <v>0.0007126377313397825</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.004215463995933533</v>
+        <v>3.647099947556853e-05</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.0108760166913271</v>
+        <v>0.0001801357429940253</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.006304340902715921</v>
+        <v>5.405381671153009e-06</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.008975399658083916</v>
+        <v>0.00137782352976501</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.004812882281839848</v>
+        <v>0.0004449523403309286</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.002363878767937422</v>
+        <v>8.154584065778181e-05</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.005915314424782991</v>
+        <v>3.184028537361883e-05</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.005387183744460344</v>
+        <v>0.0004886694950982928</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.001115404535084963</v>
+        <v>0.0001636055676499382</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.004741198848932981</v>
+        <v>0.0004563881375361234</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.01138511206954718</v>
+        <v>0.0005280541954562068</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.0009543765336275101</v>
+        <v>0.0005229422822594643</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.0267860684543848</v>
+        <v>0.001453734119422734</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0002481780829839408</v>
+        <v>0.0004011273849755526</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.006985010113567114</v>
+        <v>0.001026006881147623</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.01106463745236397</v>
+        <v>0.0003472799435257912</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.005221820436418056</v>
+        <v>0.002140005119144917</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.001029689097777009</v>
+        <v>0.0004187294980511069</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.002752978820353746</v>
+        <v>0.0001246848842129111</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.003071294166147709</v>
+        <v>0.0003747380105778575</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.006539714056998491</v>
+        <v>3.123295027762651e-05</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.0002345937537029386</v>
+        <v>0.0002996740804519504</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.01023128721863031</v>
+        <v>7.874889706727117e-05</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.009709790349006653</v>
+        <v>0.0004879773478023708</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.0009020162979140878</v>
+        <v>9.049353684531525e-05</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.004451264161616564</v>
+        <v>0.001014806097373366</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.00540497899055481</v>
+        <v>0.001591922249644995</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.004529659170657396</v>
+        <v>0.0003063000331167132</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.002175256377086043</v>
+        <v>0.0003270978631917387</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.007098990492522717</v>
+        <v>0.0007799752056598663</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.001066537108272314</v>
+        <v>0.0006577633321285248</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.001944878371432424</v>
+        <v>0.0003007850318681449</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.001226095715537667</v>
+        <v>0.0002860113745555282</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.002980661578476429</v>
+        <v>0.0001808221713872626</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.002384447026997805</v>
+        <v>0.001277639996260405</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.001100036199204624</v>
+        <v>0.0007337946444749832</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.0002201646566390991</v>
+        <v>0.0003254147013649344</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.008278915658593178</v>
+        <v>0.0001636720553506166</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.005381624214351177</v>
+        <v>0.0004628405440598726</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.005919369868934155</v>
+        <v>0.001528709661215544</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.007982298731803894</v>
+        <v>0.0005105340969748795</v>
       </c>
       <c r="EK12" t="n">
-        <v>8.204288315027952e-05</v>
+        <v>0.0001595342182554305</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.004630856215953827</v>
+        <v>8.96836572792381e-05</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.0008888444863259792</v>
+        <v>0.0002688031236175448</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.003955799620598555</v>
+        <v>7.851231202948838e-05</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.0006084069609642029</v>
+        <v>7.771745731588453e-05</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.01078957878053188</v>
+        <v>0.000487071491079405</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.004311901982873678</v>
+        <v>4.759231524076313e-05</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.009080653078854084</v>
+        <v>0.001216369913890958</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.0003792662173509598</v>
+        <v>0.0002159673458663747</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.01208813302218914</v>
+        <v>0.0002824235416483134</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.01181371696293354</v>
+        <v>0.0003477257560007274</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.009547595866024494</v>
+        <v>0.000938325421884656</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.002250329591333866</v>
+        <v>0.001193528645671904</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.002155648777261376</v>
+        <v>7.839151658117771e-05</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.01157635357230902</v>
+        <v>0.0004276381805539131</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.003832676680758595</v>
+        <v>8.492310007568449e-05</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.008753322064876556</v>
+        <v>0.001536272931843996</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.002594696125015616</v>
+        <v>0.0003166717942804098</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.001211509690620005</v>
+        <v>0.0002629514201544225</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.006529228296130896</v>
+        <v>9.275352931581438e-05</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.003979197237640619</v>
+        <v>0.0005714060389436781</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.00260121189057827</v>
+        <v>3.759278479265049e-05</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.00235511502251029</v>
+        <v>0.0004610455653164536</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.005913644097745419</v>
+        <v>0.0001325892517343163</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.006865194067358971</v>
+        <v>0.0003374902298673987</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.009098945185542107</v>
+        <v>0.000386506988434121</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.002416023518890142</v>
+        <v>5.657022484228946e-05</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.008706581778824329</v>
+        <v>0.0003299903764855117</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.002205409109592438</v>
+        <v>0.0004291419754736125</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.004087039735168219</v>
+        <v>0.000508840661495924</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.002963775070384145</v>
+        <v>4.612954217009246e-05</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.006181529257446527</v>
+        <v>0.0002548579359427094</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.002166518941521645</v>
+        <v>0.0006705065025016665</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.02274350821971893</v>
+        <v>0.001160478685051203</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.01098714116960764</v>
+        <v>0.0003806512686423957</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.0117512010037899</v>
+        <v>0.0003294629277661443</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.004406608641147614</v>
+        <v>0.0001614401116967201</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.009499370120465755</v>
+        <v>0.0006369423354044557</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.001436852384358644</v>
+        <v>0.001981099369004369</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.001823825179599226</v>
+        <v>0.0004437287570908666</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.005898008123040199</v>
+        <v>4.876834282185882e-06</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.001638937974348664</v>
+        <v>0.0001566895807627589</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.002572251483798027</v>
+        <v>0.0003121201007161289</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.0002250677353003994</v>
+        <v>0.0009644704405218363</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.002935422118753195</v>
+        <v>0.0005248989327810705</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.0136149674654007</v>
+        <v>0.00104407244361937</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.03602393716573715</v>
+        <v>0.0006647713016718626</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.004150158725678921</v>
+        <v>0.000564121815841645</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.004616071470081806</v>
+        <v>0.0004220721893943846</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.07984907180070877</v>
+        <v>0.0008252733387053013</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1313178837299347</v>
+        <v>0.001830965047702193</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01280645187944174</v>
+        <v>0.005275976844131947</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1059830263257027</v>
+        <v>0.0008751907153055072</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1893638223409653</v>
+        <v>0.001811901456676424</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4287547767162323</v>
+        <v>0.01171902474015951</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01905406638979912</v>
+        <v>0.001060392125509679</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2626330256462097</v>
+        <v>0.006002514157444239</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02335195429623127</v>
+        <v>0.004640650004148483</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01697497814893723</v>
+        <v>6.786175072193146e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1822905242443085</v>
+        <v>0.0004869211697950959</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04317759722471237</v>
+        <v>0.007057939656078815</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01753582060337067</v>
+        <v>0.0003898243885487318</v>
       </c>
       <c r="N13" t="n">
-        <v>0.05838420242071152</v>
+        <v>0.00608881376683712</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3256110548973083</v>
+        <v>0.0127484742552042</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0406917929649353</v>
+        <v>0.001568595413118601</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2317993193864822</v>
+        <v>0.006157321389764547</v>
       </c>
       <c r="R13" t="n">
-        <v>0.01060920301824808</v>
+        <v>0.005332683213055134</v>
       </c>
       <c r="S13" t="n">
-        <v>0.02610969357192516</v>
+        <v>0.001106363371945918</v>
       </c>
       <c r="T13" t="n">
-        <v>0.02934281155467033</v>
+        <v>0.002579858526587486</v>
       </c>
       <c r="U13" t="n">
-        <v>0.004352718591690063</v>
+        <v>0.002182223601266742</v>
       </c>
       <c r="V13" t="n">
-        <v>0.01563965156674385</v>
+        <v>0.002614200115203857</v>
       </c>
       <c r="W13" t="n">
-        <v>0.176562562584877</v>
+        <v>0.003231218550354242</v>
       </c>
       <c r="X13" t="n">
-        <v>0.05387311056256294</v>
+        <v>0.002640365855768323</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.03218524158000946</v>
+        <v>0.0004201068077236414</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.03135230764746666</v>
+        <v>0.00110327429138124</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.01233166269958019</v>
+        <v>0.000149247411172837</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.001238568685948849</v>
+        <v>0.001036530593410134</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.03832683339715004</v>
+        <v>0.0007282562437467277</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.01935972273349762</v>
+        <v>0.002414416754618287</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.002316227182745934</v>
+        <v>0.003325381549075246</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01202598959207535</v>
+        <v>0.005091971717774868</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.03141993656754494</v>
+        <v>0.005891399458050728</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.03488952293992043</v>
+        <v>0.00236966204829514</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.06941112130880356</v>
+        <v>0.0006678034551441669</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.01682641357183456</v>
+        <v>0.00109934713691473</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.004436028189957142</v>
+        <v>7.601207471452653e-05</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.008799322880804539</v>
+        <v>0.004483299795538187</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.01755320839583874</v>
+        <v>0.000795366708189249</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.01783983409404755</v>
+        <v>0.001386827323585749</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.01307032629847527</v>
+        <v>0.001839389093220234</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.01002466678619385</v>
+        <v>0.00198626471683383</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.01110009755939245</v>
+        <v>0.0003202827647328377</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.05577702075242996</v>
+        <v>0.001025742967613041</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.003252721391618252</v>
+        <v>0.00136229139752686</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.0391525998711586</v>
+        <v>0.001924842596054077</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.03680342435836792</v>
+        <v>0.01340259611606598</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.005380358546972275</v>
+        <v>0.002622280968353152</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.1489124596118927</v>
+        <v>0.0002445644931867719</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.2063462138175964</v>
+        <v>0.0008464837446808815</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.2685928344726562</v>
+        <v>0.007489372976124287</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.05534648150205612</v>
+        <v>6.696089985780418e-05</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.02568520978093147</v>
+        <v>0.002626446541398764</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.02207320742309093</v>
+        <v>0.0007462092908099294</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.06069327890872955</v>
+        <v>0.002463388489559293</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.07410114258527756</v>
+        <v>0.004322412423789501</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.02185932733118534</v>
+        <v>0.0003254800685681403</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.05744060873985291</v>
+        <v>0.002329249866306782</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.008257737383246422</v>
+        <v>0.006439259275794029</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.04786355420947075</v>
+        <v>0.003384793177247047</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.03277724236249924</v>
+        <v>0.0005876653594896197</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.111870214343071</v>
+        <v>0.0008976721437647939</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.0201856829226017</v>
+        <v>0.0004170665051788092</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.01742635481059551</v>
+        <v>0.001626962912268937</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0125146321952343</v>
+        <v>0.001198096433654428</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.006494540721178055</v>
+        <v>0.004546030424535275</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.1459596455097198</v>
+        <v>0.001108227879740298</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.05954015254974365</v>
+        <v>0.002252268837764859</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.01850247941911221</v>
+        <v>0.001143017201684415</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.01704724133014679</v>
+        <v>0.001143873087130487</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.09097295999526978</v>
+        <v>0.002937306649982929</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.009711407124996185</v>
+        <v>0.0002444167621433735</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.001695211743935943</v>
+        <v>0.0007899246411398053</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.03386001661419868</v>
+        <v>0.005693505518138409</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.01469942182302475</v>
+        <v>0.001887097023427486</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.09721613675355911</v>
+        <v>0.003324316116049886</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.1016914397478104</v>
+        <v>0.0006245195399969816</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.2124709486961365</v>
+        <v>0.006117044948041439</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.05133181810379028</v>
+        <v>0.001120575703680515</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.009814415127038956</v>
+        <v>0.00167596829123795</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.01804773509502411</v>
+        <v>0.000389774446375668</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.009551852010190487</v>
+        <v>0.0003667509008664638</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.005809896625578403</v>
+        <v>0.0007914398447610438</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.01359759178012609</v>
+        <v>0.002549233846366405</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.00265734875574708</v>
+        <v>0.0002014466736000031</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.05491247773170471</v>
+        <v>0.001288026105612516</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.08032988011837006</v>
+        <v>0.002604212379083037</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.02717622742056847</v>
+        <v>0.0008916248334571719</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.04739788919687271</v>
+        <v>0.0007177661755122244</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.001656370237469673</v>
+        <v>0.0003564208745956421</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.0005665298085659742</v>
+        <v>0.0002542767324484885</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.07689189910888672</v>
+        <v>0.005168596282601357</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.03656475245952606</v>
+        <v>6.273869075812399e-05</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.07758799195289612</v>
+        <v>0.0004871055425610393</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.1110090091824532</v>
+        <v>0.008000245317816734</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.06455405056476593</v>
+        <v>0.003706625662744045</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.07948438078165054</v>
+        <v>0.0006697378121316433</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.0927603542804718</v>
+        <v>0.004172703716903925</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.01365331374108791</v>
+        <v>0.002142477780580521</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.01141815353184938</v>
+        <v>0.0005320351338014007</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.01353009417653084</v>
+        <v>0.0001860874472185969</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.01263293903321028</v>
+        <v>0.002428870880976319</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.004024934489279985</v>
+        <v>7.472354627680033e-05</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.04548400267958641</v>
+        <v>0.001583196106366813</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.08634717017412186</v>
+        <v>0.002739649498835206</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.009873004630208015</v>
+        <v>0.0007775429403409362</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.03821878880262375</v>
+        <v>0.0003503147745504975</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.01912901178002357</v>
+        <v>0.0003129062242805958</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.09478403627872467</v>
+        <v>0.001358787296339869</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.03971359133720398</v>
+        <v>0.002827141433954239</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.01626895368099213</v>
+        <v>0.003860144410282373</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.1705837845802307</v>
+        <v>0.002739330288022757</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.004438461735844612</v>
+        <v>0.002048379508778453</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0670275092124939</v>
+        <v>0.003176940139383078</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.07188808917999268</v>
+        <v>0.0008938236860558391</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.03448888659477234</v>
+        <v>0.00206075282767415</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.05945127829909325</v>
+        <v>0.0005847378633916378</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.07453681528568268</v>
+        <v>0.0006443628226406872</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.04992692917585373</v>
+        <v>0.002931970171630383</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.02094865590333939</v>
+        <v>0.0007481657667085528</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.003817204385995865</v>
+        <v>0.002298301784321666</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.1049003973603249</v>
+        <v>0.00223659654147923</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.1148869916796684</v>
+        <v>0.004189086612313986</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.08216360211372375</v>
+        <v>3.096193540841341e-05</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.02263748459517956</v>
+        <v>0.001285745529457927</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.02100412733852863</v>
+        <v>0.0004478300106711686</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.002497170818969607</v>
+        <v>0.002377588069066405</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.04324372857809067</v>
+        <v>0.001439533196389675</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.02807883732020855</v>
+        <v>0.001554411137476563</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.04907479137182236</v>
+        <v>0.0006905277259647846</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.07633250206708908</v>
+        <v>0.001433031866326928</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.05605126172304153</v>
+        <v>0.003284271573647857</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.0339653342962265</v>
+        <v>0.0001194744036183693</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.02647986635565758</v>
+        <v>0.0003160735941492021</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.04426342621445656</v>
+        <v>0.0006755394861102104</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.004130061715841293</v>
+        <v>0.001644724048674107</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.05077999830245972</v>
+        <v>0.0002286452800035477</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.03934148699045181</v>
+        <v>0.002141187433153391</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.06889879703521729</v>
+        <v>0.0003436139668338001</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.03561136871576309</v>
+        <v>0.001851800596341491</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.05237539112567902</v>
+        <v>0.000234639213886112</v>
       </c>
       <c r="EL13" t="n">
-        <v>2.900324761867523e-05</v>
+        <v>0.0003662323579192162</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.03211187943816185</v>
+        <v>0.001210068352520466</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.01258417218923569</v>
+        <v>9.978967864299193e-05</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.04651117324829102</v>
+        <v>4.570119199343026e-05</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.004381501115858555</v>
+        <v>0.001041619223542511</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.006607882678508759</v>
+        <v>0.002094059949740767</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.05667536333203316</v>
+        <v>2.478084934409708e-05</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.05169834196567535</v>
+        <v>0.001837097108364105</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.00487663596868515</v>
+        <v>0.002055097604170442</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.01087648421525955</v>
+        <v>0.001304503879509866</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.1771194338798523</v>
+        <v>0.001603267854079604</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.05108082666993141</v>
+        <v>0.0001481591025367379</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.02157711423933506</v>
+        <v>0.0003236424236092716</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.009530059993267059</v>
+        <v>0.0008668189402669668</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.004751275293529034</v>
+        <v>0.002324135042726994</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.001818065764382482</v>
+        <v>0.0001646676100790501</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.06244246661663055</v>
+        <v>0.001197368605062366</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.07159742712974548</v>
+        <v>0.003140377346426249</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.02629301324486732</v>
+        <v>0.001339823938906193</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.05112831294536591</v>
+        <v>0.0001496353361289948</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.01307496055960655</v>
+        <v>5.388879799284041e-05</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.04252658039331436</v>
+        <v>0.001263614743947983</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.01115363463759422</v>
+        <v>0.002637721132487059</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.000405140221118927</v>
+        <v>0.001972880214452744</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.1313239634037018</v>
+        <v>0.0042233532294631</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.03843730315566063</v>
+        <v>6.522628245875239e-05</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.005143330432474613</v>
+        <v>0.002888956107199192</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.01301715895533562</v>
+        <v>0.001585989142768085</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0253559835255146</v>
+        <v>0.00108295539394021</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.0229883436113596</v>
+        <v>0.001351544400677085</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.02002113871276379</v>
+        <v>6.492657121270895e-05</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.1780639737844467</v>
+        <v>0.005181542597711086</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.02878568693995476</v>
+        <v>0.00408269464969635</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.01605141721665859</v>
+        <v>0.003158437088131905</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.2540574967861176</v>
+        <v>0.003646065481007099</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.05167762935161591</v>
+        <v>0.004555041436105967</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.04705264046788216</v>
+        <v>0.002232361352071166</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.1542165726423264</v>
+        <v>0.00475229462608695</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.06768960505723953</v>
+        <v>0.0006653523887507617</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.03723413869738579</v>
+        <v>0.0005052216583862901</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.1005433574318886</v>
+        <v>0.002258503576740623</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.00622502388432622</v>
+        <v>0.003804830368608236</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.04713339731097221</v>
+        <v>0.002407723572105169</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.1191584467887878</v>
+        <v>0.001914476742967963</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.01896688528358936</v>
+        <v>0.0009172055288217962</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.08027587831020355</v>
+        <v>0.0002458514936733991</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.05921689420938492</v>
+        <v>0.0006692790193483233</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.008724368177354336</v>
+        <v>0.0001194512587971985</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.002049851231276989</v>
+        <v>0.4281841516494751</v>
       </c>
       <c r="B14" t="n">
-        <v>0.001804561004973948</v>
+        <v>0.0752967894077301</v>
       </c>
       <c r="C14" t="n">
-        <v>0.001227384665980935</v>
+        <v>0.8742455244064331</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00995166040956974</v>
+        <v>0.9257097244262695</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001813392038457096</v>
+        <v>0.0169086828827858</v>
       </c>
       <c r="F14" t="n">
-        <v>0.004038434941321611</v>
+        <v>0.3193708956241608</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001355163985863328</v>
+        <v>0.3151006102561951</v>
       </c>
       <c r="H14" t="n">
-        <v>0.006221694406121969</v>
+        <v>0.257086843252182</v>
       </c>
       <c r="I14" t="n">
-        <v>9.410228813067079e-05</v>
+        <v>0.5393690466880798</v>
       </c>
       <c r="J14" t="n">
-        <v>0.004632493015378714</v>
+        <v>0.3131512403488159</v>
       </c>
       <c r="K14" t="n">
-        <v>0.002159595489501953</v>
+        <v>0.1139664053916931</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001885853824205697</v>
+        <v>0.6657343506813049</v>
       </c>
       <c r="M14" t="n">
-        <v>0.006316752173006535</v>
+        <v>1.129791498184204</v>
       </c>
       <c r="N14" t="n">
-        <v>0.001749851973727345</v>
+        <v>0.2538396716117859</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0002608024224173278</v>
+        <v>0.318884015083313</v>
       </c>
       <c r="P14" t="n">
-        <v>0.002767553087323904</v>
+        <v>0.2819150686264038</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0008389904396608472</v>
+        <v>0.03217506408691406</v>
       </c>
       <c r="R14" t="n">
-        <v>0.004966915119439363</v>
+        <v>0.4331784546375275</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0001450438285246491</v>
+        <v>0.01829979941248894</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0002581378212198615</v>
+        <v>0.1028768122196198</v>
       </c>
       <c r="U14" t="n">
-        <v>0.001901428448036313</v>
+        <v>0.1624059528112411</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0007059037452563643</v>
+        <v>0.1456775367259979</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0008604481117799878</v>
+        <v>0.3979862630367279</v>
       </c>
       <c r="X14" t="n">
-        <v>0.00111133698374033</v>
+        <v>0.224195808172226</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.001472016330808401</v>
+        <v>0.09860144555568695</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0005138835404068232</v>
+        <v>0.01412777230143547</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.001719102961942554</v>
+        <v>0.03906548023223877</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.003808527253568172</v>
+        <v>0.1753735691308975</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.006058420985937119</v>
+        <v>0.1824145466089249</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0001666978059802204</v>
+        <v>0.04316867515444756</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.001901664538308978</v>
+        <v>0.2426595985889435</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0005380657385103405</v>
+        <v>0.4934700727462769</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.003064497373998165</v>
+        <v>0.1488228887319565</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.001455782330594957</v>
+        <v>0.1657994240522385</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.001487283734604716</v>
+        <v>0.1399463415145874</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0008862551185302436</v>
+        <v>0.1004174649715424</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0007733392994850874</v>
+        <v>0.07417276501655579</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.0001435635203961283</v>
+        <v>0.002789489924907684</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0001057950867107138</v>
+        <v>0.2175337970256805</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0002278174797538668</v>
+        <v>0.4064886569976807</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.002120885299518704</v>
+        <v>0.08938413113355637</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.001966724870726466</v>
+        <v>0.1634306311607361</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.002232299419119954</v>
+        <v>0.3392409384250641</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.0003359437978360802</v>
+        <v>0.1263884454965591</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.001325168297626078</v>
+        <v>0.1694660484790802</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.001419164822436869</v>
+        <v>0.03567671775817871</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.004922333639115095</v>
+        <v>0.2818811535835266</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.004170607775449753</v>
+        <v>0.4908450245857239</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.004594468511641026</v>
+        <v>0.6725404262542725</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.004756365902721882</v>
+        <v>0.1973328739404678</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.001345184398815036</v>
+        <v>0.4076168537139893</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.001673536491580307</v>
+        <v>0.2346484214067459</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.002622790168970823</v>
+        <v>0.06890667974948883</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.001269537024199963</v>
+        <v>0.3490062355995178</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.004980246536433697</v>
+        <v>0.4310716688632965</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.004340349696576595</v>
+        <v>0.1637648940086365</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.001597003079950809</v>
+        <v>0.2163398861885071</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.00157927384134382</v>
+        <v>0.3320936262607574</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.002953311195597053</v>
+        <v>0.5830969214439392</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.001537294359877706</v>
+        <v>0.2649149298667908</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.003609573468565941</v>
+        <v>0.2650190889835358</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.004239074420183897</v>
+        <v>0.1015968546271324</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.0003962230985052884</v>
+        <v>0.01834132522344589</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.001152057200670242</v>
+        <v>0.03176400437951088</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.0004175739013589919</v>
+        <v>0.2098475396633148</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.002784265903756022</v>
+        <v>0.06106054037809372</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.002272145822644234</v>
+        <v>0.2872170805931091</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.003299937816336751</v>
+        <v>0.04619114100933075</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.002581986365839839</v>
+        <v>0.00742918998003006</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.0003950212267227471</v>
+        <v>0.01932342350482941</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.001548242755234241</v>
+        <v>0.174875944852829</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.003363867057487369</v>
+        <v>0.1051482856273651</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.0009440346038900316</v>
+        <v>0.02269804105162621</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.002788817277178168</v>
+        <v>0.04665526002645493</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.001687205396592617</v>
+        <v>0.2037912756204605</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.0007751989178359509</v>
+        <v>0.6642157435417175</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.002827589400112629</v>
+        <v>0.3332488536834717</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.001190963666886091</v>
+        <v>0.02555450052022934</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.001896882313303649</v>
+        <v>0.1167993322014809</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.0007279038545675576</v>
+        <v>0.1814393401145935</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.00107725802809</v>
+        <v>0.07913734763860703</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.0001844237849581987</v>
+        <v>0.08918331563472748</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.0005007701693102717</v>
+        <v>0.256607323884964</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.00051791564328596</v>
+        <v>0.1809665560722351</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.001345818862318993</v>
+        <v>0.338166207075119</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.0009989391546696424</v>
+        <v>0.002412691712379456</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.001528344349935651</v>
+        <v>0.06692323088645935</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.0006550823454745114</v>
+        <v>0.009101617150008678</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.0009393451036885381</v>
+        <v>0.03387514129281044</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.0007637334638275206</v>
+        <v>0.05267012119293213</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.002703857142478228</v>
+        <v>0.09125298261642456</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.000283269357169047</v>
+        <v>0.184747114777565</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.0006861401489004493</v>
+        <v>0.02893465012311935</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.001056535867974162</v>
+        <v>0.2382301092147827</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.00411664554849267</v>
+        <v>0.6383869051933289</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.002222927985712886</v>
+        <v>0.2077346444129944</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.00260787270963192</v>
+        <v>0.104320727288723</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.005021821707487106</v>
+        <v>0.05334282666444778</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0005267651868052781</v>
+        <v>0.4478561282157898</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.0005815901677124202</v>
+        <v>0.05993670597672462</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.648442750796676e-05</v>
+        <v>0.2062988430261612</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.0002925735607277602</v>
+        <v>0.1623775810003281</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.00166201707907021</v>
+        <v>0.308944970369339</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.0007725700852461159</v>
+        <v>0.0124692702665925</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.0009654133464209735</v>
+        <v>0.08794961869716644</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.00114625773858279</v>
+        <v>0.03434387966990471</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.0009345153230242431</v>
+        <v>0.03308608010411263</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.001215543947182596</v>
+        <v>0.02977155521512032</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.001398872118443251</v>
+        <v>0.006964033003896475</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.0008179516298696399</v>
+        <v>0.2877963483333588</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.002867405535653234</v>
+        <v>0.5344750881195068</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.00405835872516036</v>
+        <v>0.2479840964078903</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.001428682473488152</v>
+        <v>0.1419408023357391</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.00135060481261462</v>
+        <v>0.2482947260141373</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.001708849333226681</v>
+        <v>0.1122611612081528</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.006194713991135359</v>
+        <v>0.4716717004776001</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.0002073708164971322</v>
+        <v>0.2348402738571167</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0005080843111500144</v>
+        <v>0.1349946260452271</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.001202599843963981</v>
+        <v>0.07652898132801056</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.0009799007093533874</v>
+        <v>0.2045692056417465</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.001439489889889956</v>
+        <v>0.02114995568990707</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.000534077116753906</v>
+        <v>0.2623054981231689</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.001808377215638757</v>
+        <v>0.2390394806861877</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.0006355124060064554</v>
+        <v>0.02664918079972267</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.002467719838023186</v>
+        <v>0.09067992866039276</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.001402626396156847</v>
+        <v>0.4629848301410675</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.002305875066667795</v>
+        <v>0.1149860322475433</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.001708001946099102</v>
+        <v>0.2551973760128021</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.002359414706006646</v>
+        <v>0.2925426661968231</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.001235769828781486</v>
+        <v>0.1578153967857361</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.002162105171009898</v>
+        <v>0.02626338973641396</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.001347304903902113</v>
+        <v>0.1023976877331734</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.0002001321408897638</v>
+        <v>0.07451876252889633</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.001137744053266943</v>
+        <v>0.3484433591365814</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.0003113941638730466</v>
+        <v>0.2917088568210602</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.000544019800145179</v>
+        <v>0.02631537243723869</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.0002244333154521883</v>
+        <v>0.192094549536705</v>
       </c>
       <c r="EH14" t="n">
-        <v>6.664422107860446e-05</v>
+        <v>0.09033013135194778</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.001544723054394126</v>
+        <v>0.343894749879837</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.00302239041775465</v>
+        <v>0.08533982932567596</v>
       </c>
       <c r="EK14" t="n">
-        <v>3.579791882657446e-05</v>
+        <v>0.02632173150777817</v>
       </c>
       <c r="EL14" t="n">
-        <v>5.629539373330772e-05</v>
+        <v>0.04866614937782288</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.0003541074693202972</v>
+        <v>0.01240129768848419</v>
       </c>
       <c r="EN14" t="n">
-        <v>8.951705967774615e-05</v>
+        <v>0.09878921508789062</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.001283269608393312</v>
+        <v>0.004229737911373377</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.002725515747442842</v>
+        <v>0.2613890171051025</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0001426782109774649</v>
+        <v>0.05712845176458359</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.0002039654063992202</v>
+        <v>0.2853415608406067</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.002112613525241613</v>
+        <v>0.1406744420528412</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.0016956168692559</v>
+        <v>0.3405739665031433</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.0005798067431896925</v>
+        <v>0.1399947106838226</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.002422013320028782</v>
+        <v>0.05884188413619995</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.004216479137539864</v>
+        <v>0.1588600873947144</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.0004849493852816522</v>
+        <v>0.08678429573774338</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0003726706490851939</v>
+        <v>0.2363384366035461</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.000909829861484468</v>
+        <v>0.1736971884965897</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.001511769252829254</v>
+        <v>0.3804468214511871</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.0003891079104505479</v>
+        <v>0.01760182343423367</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.0007103260140866041</v>
+        <v>0.002507343888282776</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0002810264122672379</v>
+        <v>0.05227342247962952</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.001193438656628132</v>
+        <v>0.02739705517888069</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.001083198701962829</v>
+        <v>0.01554965414106846</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.00122732063755393</v>
+        <v>0.04220712184906006</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.000590842217206955</v>
+        <v>0.08964952081441879</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.00395026383921504</v>
+        <v>0.1997639983892441</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.001894753659144044</v>
+        <v>0.1406252384185791</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.00187098584137857</v>
+        <v>0.1150560081005096</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.004892983473837376</v>
+        <v>0.06073843315243721</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.002496953587979078</v>
+        <v>0.06543029099702835</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.001129340613260865</v>
+        <v>0.0955628827214241</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.001255280920304358</v>
+        <v>0.1461185812950134</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.0001975542982108891</v>
+        <v>0.2983100116252899</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.003317428752779961</v>
+        <v>0.4504666328430176</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.005185297224670649</v>
+        <v>0.315138578414917</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.002817282918840647</v>
+        <v>0.2530748546123505</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.008066987618803978</v>
+        <v>0.1308944821357727</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.0009705931879580021</v>
+        <v>0.133461058139801</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.00402755755931139</v>
+        <v>0.1691355109214783</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.002276567276567221</v>
+        <v>0.2377052158117294</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.0006480022566393018</v>
+        <v>0.1008747443556786</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.001135426573455334</v>
+        <v>0.07051115483045578</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.001308147562667727</v>
+        <v>0.3748433291912079</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.002409767359495163</v>
+        <v>0.1521445512771606</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.004008106421679258</v>
+        <v>0.3170185387134552</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.004129801411181688</v>
+        <v>0.3074464499950409</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.002561149187386036</v>
+        <v>0.1835982352495193</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.005365269724279642</v>
+        <v>0.2776073515415192</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.0004657344543375075</v>
+        <v>0.07247795164585114</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.002914994023740292</v>
+        <v>0.1466462463140488</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3.377409185656433e-10</v>
+        <v>0.1384794116020203</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658351482333956e-11</v>
+        <v>0.02323295921087265</v>
       </c>
       <c r="C15" t="n">
-        <v>1.552476723565288e-11</v>
+        <v>0.02104642055928707</v>
       </c>
       <c r="D15" t="n">
-        <v>5.513442827287385e-11</v>
+        <v>0.04923626780509949</v>
       </c>
       <c r="E15" t="n">
-        <v>1.572964675178312e-10</v>
+        <v>0.02905705757439137</v>
       </c>
       <c r="F15" t="n">
-        <v>1.817552774951992e-10</v>
+        <v>0.08753979206085205</v>
       </c>
       <c r="G15" t="n">
-        <v>1.038173713663326e-11</v>
+        <v>0.0243291761726141</v>
       </c>
       <c r="H15" t="n">
-        <v>7.010725333600476e-11</v>
+        <v>0.01840400137007236</v>
       </c>
       <c r="I15" t="n">
-        <v>9.741753237424433e-11</v>
+        <v>0.01511944830417633</v>
       </c>
       <c r="J15" t="n">
-        <v>3.532888981361282e-10</v>
+        <v>0.1524823755025864</v>
       </c>
       <c r="K15" t="n">
-        <v>5.173787440138078e-11</v>
+        <v>0.03159132599830627</v>
       </c>
       <c r="L15" t="n">
-        <v>7.199063567497888e-11</v>
+        <v>0.03388958424329758</v>
       </c>
       <c r="M15" t="n">
-        <v>1.599747001534979e-10</v>
+        <v>0.01953356899321079</v>
       </c>
       <c r="N15" t="n">
-        <v>4.394614533387298e-11</v>
+        <v>0.04779648780822754</v>
       </c>
       <c r="O15" t="n">
-        <v>1.954612582899529e-10</v>
+        <v>0.08876199275255203</v>
       </c>
       <c r="P15" t="n">
-        <v>3.943101400949445e-11</v>
+        <v>0.02497295662760735</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.166026882472366e-12</v>
+        <v>0.03323235362768173</v>
       </c>
       <c r="R15" t="n">
-        <v>9.189260463671189e-11</v>
+        <v>0.02011879533529282</v>
       </c>
       <c r="S15" t="n">
-        <v>4.687289792415505e-11</v>
+        <v>0.004233094863593578</v>
       </c>
       <c r="T15" t="n">
-        <v>9.037663672994967e-11</v>
+        <v>5.854340270161629e-05</v>
       </c>
       <c r="U15" t="n">
-        <v>2.974660448518129e-13</v>
+        <v>0.02420222200453281</v>
       </c>
       <c r="V15" t="n">
-        <v>1.525364279331143e-10</v>
+        <v>0.004692196846008301</v>
       </c>
       <c r="W15" t="n">
-        <v>4.131332775880736e-11</v>
+        <v>0.02091658115386963</v>
       </c>
       <c r="X15" t="n">
-        <v>3.236655388150211e-11</v>
+        <v>0.0297018401324749</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.922830033558199e-11</v>
+        <v>0.03654145449399948</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.02439841604652e-12</v>
+        <v>0.001972632249817252</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.694062070125348e-11</v>
+        <v>0.004059175960719585</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.225470155381437e-11</v>
+        <v>0.03384461253881454</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.526218289058193e-11</v>
+        <v>0.04293081909418106</v>
       </c>
       <c r="AD15" t="n">
-        <v>5.499797839370046e-11</v>
+        <v>0.007726685144007206</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.909470060707964e-11</v>
+        <v>0.02328744530677795</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.54600290902529e-12</v>
+        <v>0.02983329817652702</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.59943672090246e-11</v>
+        <v>0.03001860529184341</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.287138699599069e-11</v>
+        <v>0.01115008443593979</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.321793507980118e-10</v>
+        <v>0.01779326796531677</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4.101854619853462e-11</v>
+        <v>0.001254880335181952</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.729422070302245e-11</v>
+        <v>0.009370162151753902</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.187114295753133e-11</v>
+        <v>0.008587436750531197</v>
       </c>
       <c r="AM15" t="n">
-        <v>7.379376623650735e-12</v>
+        <v>0.02540544234216213</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.790727635619938e-11</v>
+        <v>0.004253781400620937</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.768697133197605e-10</v>
+        <v>0.03332846239209175</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.783127374395011e-11</v>
+        <v>0.00130193738732487</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.049070552650022e-12</v>
+        <v>0.01965242810547352</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.65947835870395e-11</v>
+        <v>0.01581765525043011</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.105567452504898e-12</v>
+        <v>0.0004145727143622935</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.079989292440686e-10</v>
+        <v>0.07736088335514069</v>
       </c>
       <c r="AU15" t="n">
-        <v>8.849648791553477e-11</v>
+        <v>0.07601521909236908</v>
       </c>
       <c r="AV15" t="n">
-        <v>6.912948685711129e-11</v>
+        <v>0.03452963382005692</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.185449655105586e-10</v>
+        <v>0.009508363902568817</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.718964415253765e-10</v>
+        <v>0.002985829021781683</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.712125441422074e-10</v>
+        <v>0.06291414052248001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.639610752197541e-11</v>
+        <v>0.0232008695602417</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.695608122444298e-11</v>
+        <v>0.01073587220162153</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.225299167684213e-10</v>
+        <v>0.002995128743350506</v>
       </c>
       <c r="BC15" t="n">
-        <v>9.787252258641743e-11</v>
+        <v>0.0052629797719419</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.996623873179448e-11</v>
+        <v>0.01763029582798481</v>
       </c>
       <c r="BE15" t="n">
-        <v>3.65969268778521e-11</v>
+        <v>0.01432362571358681</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.180050915460811e-11</v>
+        <v>0.02582297846674919</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.021609186135919e-10</v>
+        <v>0.01846414618194103</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.237159762996654e-10</v>
+        <v>0.02027985826134682</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.396424989530409e-11</v>
+        <v>0.006012661382555962</v>
       </c>
       <c r="BJ15" t="n">
-        <v>4.363795783057789e-11</v>
+        <v>0.01391632482409477</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.995871854569401e-11</v>
+        <v>0.01750828698277473</v>
       </c>
       <c r="BL15" t="n">
-        <v>5.569876504463167e-11</v>
+        <v>0.01450697705149651</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.029222124193652e-10</v>
+        <v>0.06283112615346909</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.138132627702241e-11</v>
+        <v>0.0005762397195212543</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.153147195787074e-11</v>
+        <v>0.04154754430055618</v>
       </c>
       <c r="BP15" t="n">
-        <v>6.492927029366768e-11</v>
+        <v>0.03868920728564262</v>
       </c>
       <c r="BQ15" t="n">
-        <v>9.623286889581806e-11</v>
+        <v>0.01657378859817982</v>
       </c>
       <c r="BR15" t="n">
-        <v>4.610819538675148e-12</v>
+        <v>0.003315005451440811</v>
       </c>
       <c r="BS15" t="n">
-        <v>2.187255931929144e-11</v>
+        <v>0.0151203041896224</v>
       </c>
       <c r="BT15" t="n">
-        <v>1.022066199035665e-11</v>
+        <v>0.0002790961880236864</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.672743524920421e-11</v>
+        <v>0.05229571089148521</v>
       </c>
       <c r="BV15" t="n">
-        <v>1.235468671811901e-11</v>
+        <v>0.01214988809078932</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.622192906200695e-11</v>
+        <v>0.02344410121440887</v>
       </c>
       <c r="BX15" t="n">
-        <v>8.739896306675377e-11</v>
+        <v>0.0252767987549305</v>
       </c>
       <c r="BY15" t="n">
-        <v>6.271083478892603e-12</v>
+        <v>0.05494260042905807</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.253167430936841e-10</v>
+        <v>0.03523819148540497</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.098477460190431e-11</v>
+        <v>0.02924135513603687</v>
       </c>
       <c r="CB15" t="n">
-        <v>6.177008904373338e-11</v>
+        <v>0.01467278506606817</v>
       </c>
       <c r="CC15" t="n">
-        <v>5.477114595198174e-11</v>
+        <v>0.00496132904663682</v>
       </c>
       <c r="CD15" t="n">
-        <v>6.974531369108306e-11</v>
+        <v>0.03490502387285233</v>
       </c>
       <c r="CE15" t="n">
-        <v>5.348509135583157e-11</v>
+        <v>0.008115882985293865</v>
       </c>
       <c r="CF15" t="n">
-        <v>8.680511170977567e-12</v>
+        <v>0.003215349745005369</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.250123698477324e-12</v>
+        <v>0.02216823399066925</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.907418450616816e-12</v>
+        <v>0.01844923198223114</v>
       </c>
       <c r="CI15" t="n">
-        <v>4.902707059772915e-11</v>
+        <v>0.01841187849640846</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.520216244554895e-13</v>
+        <v>0.004450969863682985</v>
       </c>
       <c r="CK15" t="n">
-        <v>4.923221552655122e-12</v>
+        <v>0.004295777529478073</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.84938479061525e-11</v>
+        <v>0.000612709962297231</v>
       </c>
       <c r="CM15" t="n">
-        <v>4.099337189145125e-11</v>
+        <v>0.01278463006019592</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.028109541945099e-11</v>
+        <v>0.03387948125600815</v>
       </c>
       <c r="CO15" t="n">
-        <v>7.424595660499023e-12</v>
+        <v>0.04525754600763321</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.185238621998931e-11</v>
+        <v>0.05343836918473244</v>
       </c>
       <c r="CQ15" t="n">
-        <v>1.938175869797831e-10</v>
+        <v>0.03741062432527542</v>
       </c>
       <c r="CR15" t="n">
-        <v>6.701490057325898e-11</v>
+        <v>0.02428957633674145</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.113843475259891e-11</v>
+        <v>0.05498307943344116</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.062293565086026e-11</v>
+        <v>0.001211083144880831</v>
       </c>
       <c r="CU15" t="n">
-        <v>3.590229502581366e-11</v>
+        <v>0.02902668341994286</v>
       </c>
       <c r="CV15" t="n">
-        <v>6.289629234101923e-11</v>
+        <v>0.032704196870327</v>
       </c>
       <c r="CW15" t="n">
-        <v>4.351369958799367e-11</v>
+        <v>0.004767061211168766</v>
       </c>
       <c r="CX15" t="n">
-        <v>5.173024335280996e-12</v>
+        <v>0.007345497608184814</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.244779106179816e-11</v>
+        <v>0.01495314575731754</v>
       </c>
       <c r="CZ15" t="n">
-        <v>1.151026236129171e-11</v>
+        <v>0.01756863296031952</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.348166799892581e-11</v>
+        <v>0.02316647581756115</v>
       </c>
       <c r="DB15" t="n">
-        <v>6.152703346806732e-12</v>
+        <v>0.00390520365908742</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.222080158764683e-11</v>
+        <v>0.0005423339316621423</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.37356835575131e-11</v>
+        <v>0.002135728020220995</v>
       </c>
       <c r="DE15" t="n">
-        <v>2.140578131415438e-10</v>
+        <v>0.0589914433658123</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.517702907793961e-10</v>
+        <v>0.009609033353626728</v>
       </c>
       <c r="DG15" t="n">
-        <v>6.123195700480366e-11</v>
+        <v>0.01024221442639828</v>
       </c>
       <c r="DH15" t="n">
-        <v>2.436635893054984e-10</v>
+        <v>0.0423073023557663</v>
       </c>
       <c r="DI15" t="n">
-        <v>1.832265311696446e-10</v>
+        <v>0.09334701299667358</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.580430057657178e-11</v>
+        <v>0.02573280408978462</v>
       </c>
       <c r="DK15" t="n">
-        <v>1.411080974289547e-10</v>
+        <v>0.001746087335050106</v>
       </c>
       <c r="DL15" t="n">
-        <v>1.401624372121546e-10</v>
+        <v>0.04374125972390175</v>
       </c>
       <c r="DM15" t="n">
-        <v>2.164590728881421e-10</v>
+        <v>0.001334588858298957</v>
       </c>
       <c r="DN15" t="n">
-        <v>8.239300908208236e-11</v>
+        <v>0.005943702068179846</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.388628101395284e-11</v>
+        <v>0.00491727888584137</v>
       </c>
       <c r="DP15" t="n">
-        <v>2.394854106690936e-11</v>
+        <v>0.002962627448141575</v>
       </c>
       <c r="DQ15" t="n">
-        <v>5.248611614772081e-11</v>
+        <v>0.004202267155051231</v>
       </c>
       <c r="DR15" t="n">
-        <v>5.715495438041174e-11</v>
+        <v>0.03288243338465691</v>
       </c>
       <c r="DS15" t="n">
-        <v>8.556920449986904e-11</v>
+        <v>0.000344833912095055</v>
       </c>
       <c r="DT15" t="n">
-        <v>5.201831673740109e-11</v>
+        <v>0.02285252697765827</v>
       </c>
       <c r="DU15" t="n">
-        <v>1.159148332874338e-10</v>
+        <v>0.05233044922351837</v>
       </c>
       <c r="DV15" t="n">
-        <v>5.165593300326954e-11</v>
+        <v>0.005906086415052414</v>
       </c>
       <c r="DW15" t="n">
-        <v>5.833258875931335e-11</v>
+        <v>0.008446742780506611</v>
       </c>
       <c r="DX15" t="n">
-        <v>1.038774552486466e-10</v>
+        <v>0.0249212384223938</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.844781603148164e-11</v>
+        <v>0.03916715085506439</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.099923789884329e-11</v>
+        <v>0.07664627581834793</v>
       </c>
       <c r="EA15" t="n">
-        <v>3.205939680395176e-11</v>
+        <v>0.007321937009692192</v>
       </c>
       <c r="EB15" t="n">
-        <v>4.268017189668072e-11</v>
+        <v>0.01265041250735521</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.019746779020505e-12</v>
+        <v>0.01274832151830196</v>
       </c>
       <c r="ED15" t="n">
-        <v>1.784935046988956e-11</v>
+        <v>0.02601088397204876</v>
       </c>
       <c r="EE15" t="n">
-        <v>8.968068648806948e-11</v>
+        <v>0.03896461427211761</v>
       </c>
       <c r="EF15" t="n">
-        <v>7.462720719164651e-11</v>
+        <v>0.002159740542992949</v>
       </c>
       <c r="EG15" t="n">
-        <v>2.66049907798882e-11</v>
+        <v>0.0169770885258913</v>
       </c>
       <c r="EH15" t="n">
-        <v>1.217367873174169e-11</v>
+        <v>0.007166435942053795</v>
       </c>
       <c r="EI15" t="n">
-        <v>3.674448939561259e-11</v>
+        <v>0.0003190482966601849</v>
       </c>
       <c r="EJ15" t="n">
-        <v>2.969295642696324e-11</v>
+        <v>0.005528763402253389</v>
       </c>
       <c r="EK15" t="n">
-        <v>5.041975517650066e-11</v>
+        <v>0.02686314471065998</v>
       </c>
       <c r="EL15" t="n">
-        <v>2.601212474584447e-11</v>
+        <v>0.009839804843068123</v>
       </c>
       <c r="EM15" t="n">
-        <v>2.70720728820506e-12</v>
+        <v>0.02174743078649044</v>
       </c>
       <c r="EN15" t="n">
-        <v>3.260767003632203e-11</v>
+        <v>0.01203733123838902</v>
       </c>
       <c r="EO15" t="n">
-        <v>3.272946150212341e-11</v>
+        <v>0.009677018038928509</v>
       </c>
       <c r="EP15" t="n">
-        <v>5.24537011048487e-11</v>
+        <v>0.01319368835538626</v>
       </c>
       <c r="EQ15" t="n">
-        <v>8.208517199292942e-11</v>
+        <v>0.01612900756299496</v>
       </c>
       <c r="ER15" t="n">
-        <v>1.373709479501883e-11</v>
+        <v>0.02195507287979126</v>
       </c>
       <c r="ES15" t="n">
-        <v>7.656607292627626e-11</v>
+        <v>0.008466186933219433</v>
       </c>
       <c r="ET15" t="n">
-        <v>6.996575541151628e-11</v>
+        <v>0.001737958751618862</v>
       </c>
       <c r="EU15" t="n">
-        <v>1.030813628899452e-11</v>
+        <v>0.02561664208769798</v>
       </c>
       <c r="EV15" t="n">
-        <v>3.376525795073526e-11</v>
+        <v>0.09987012296915054</v>
       </c>
       <c r="EW15" t="n">
-        <v>6.657097789686262e-11</v>
+        <v>0.001904592616483569</v>
       </c>
       <c r="EX15" t="n">
-        <v>5.88009779756149e-11</v>
+        <v>0.02448983490467072</v>
       </c>
       <c r="EY15" t="n">
-        <v>2.518643626991945e-11</v>
+        <v>0.006155150942504406</v>
       </c>
       <c r="EZ15" t="n">
-        <v>1.219051595779952e-11</v>
+        <v>0.006242281757295132</v>
       </c>
       <c r="FA15" t="n">
-        <v>1.36046417187341e-11</v>
+        <v>0.00226277019828558</v>
       </c>
       <c r="FB15" t="n">
-        <v>3.867065955648341e-12</v>
+        <v>0.007751109078526497</v>
       </c>
       <c r="FC15" t="n">
-        <v>4.693865782168238e-11</v>
+        <v>0.02270974777638912</v>
       </c>
       <c r="FD15" t="n">
-        <v>1.331391767667167e-11</v>
+        <v>0.001658100285567343</v>
       </c>
       <c r="FE15" t="n">
-        <v>4.808723731708486e-12</v>
+        <v>0.002499729860574007</v>
       </c>
       <c r="FF15" t="n">
-        <v>1.914809977243692e-11</v>
+        <v>0.006126179825514555</v>
       </c>
       <c r="FG15" t="n">
-        <v>6.350024672752141e-11</v>
+        <v>0.08626493811607361</v>
       </c>
       <c r="FH15" t="n">
-        <v>4.534465858352377e-11</v>
+        <v>0.00168694369494915</v>
       </c>
       <c r="FI15" t="n">
-        <v>2.514599639624748e-12</v>
+        <v>0.03178177401423454</v>
       </c>
       <c r="FJ15" t="n">
-        <v>4.826283123149366e-11</v>
+        <v>0.06934276968240738</v>
       </c>
       <c r="FK15" t="n">
-        <v>3.946717258562771e-11</v>
+        <v>0.03398508951067924</v>
       </c>
       <c r="FL15" t="n">
-        <v>8.795606604161677e-11</v>
+        <v>0.02980348467826843</v>
       </c>
       <c r="FM15" t="n">
-        <v>4.471328689248377e-12</v>
+        <v>0.05063014850020409</v>
       </c>
       <c r="FN15" t="n">
-        <v>2.354932221448891e-11</v>
+        <v>0.01538052130490541</v>
       </c>
       <c r="FO15" t="n">
-        <v>5.319472293208172e-11</v>
+        <v>0.03479028865695</v>
       </c>
       <c r="FP15" t="n">
-        <v>1.050166203997449e-10</v>
+        <v>0.06855705380439758</v>
       </c>
       <c r="FQ15" t="n">
-        <v>6.900861132530522e-11</v>
+        <v>0.03720054030418396</v>
       </c>
       <c r="FR15" t="n">
-        <v>1.402171712072686e-10</v>
+        <v>0.03257147222757339</v>
       </c>
       <c r="FS15" t="n">
-        <v>1.772695462642915e-10</v>
+        <v>0.07141591608524323</v>
       </c>
       <c r="FT15" t="n">
-        <v>1.568440377575087e-10</v>
+        <v>0.005130269099026918</v>
       </c>
       <c r="FU15" t="n">
-        <v>9.885911533835667e-12</v>
+        <v>0.03489319607615471</v>
       </c>
       <c r="FV15" t="n">
-        <v>7.873142415792955e-11</v>
+        <v>0.05411790311336517</v>
       </c>
       <c r="FW15" t="n">
-        <v>9.743580248189332e-11</v>
+        <v>0.002085579792037606</v>
       </c>
       <c r="FX15" t="n">
-        <v>2.046250668907845e-11</v>
+        <v>0.006614657118916512</v>
       </c>
       <c r="FY15" t="n">
-        <v>1.547047732974871e-11</v>
+        <v>0.01937298104166985</v>
       </c>
       <c r="FZ15" t="n">
-        <v>3.461364528334343e-11</v>
+        <v>0.07818477600812912</v>
       </c>
       <c r="GA15" t="n">
-        <v>8.496468806296065e-11</v>
+        <v>0.02028215676546097</v>
       </c>
       <c r="GB15" t="n">
-        <v>1.004934850612482e-11</v>
+        <v>0.008351877331733704</v>
       </c>
       <c r="GC15" t="n">
-        <v>1.335416777159537e-10</v>
+        <v>0.02798457443714142</v>
       </c>
       <c r="GD15" t="n">
-        <v>2.178082540715831e-11</v>
+        <v>0.02567580528557301</v>
       </c>
       <c r="GE15" t="n">
-        <v>3.757399946735518e-11</v>
+        <v>0.03807947412133217</v>
       </c>
       <c r="GF15" t="n">
-        <v>2.38960552734202e-11</v>
+        <v>0.08141127973794937</v>
       </c>
       <c r="GG15" t="n">
-        <v>1.608637181793604e-11</v>
+        <v>0.002451977226883173</v>
       </c>
     </row>
   </sheetData>
